--- a/research/traditional_assets/database/data/peru/peru_apparel.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_apparel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09581320790900248</v>
+        <v>0.09556228394567091</v>
       </c>
       <c r="C2">
-        <v>102.8477452167882</v>
+        <v>102.1750278862724</v>
       </c>
       <c r="D2">
-        <v>99.90774521678816</v>
+        <v>100.3740278862724</v>
       </c>
       <c r="E2">
-        <v>-47.6</v>
+        <v>-46.461</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.139</v>
       </c>
       <c r="G2">
         <v>2.94</v>
@@ -1451,28 +1451,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0572917</v>
       </c>
       <c r="N2">
-        <v>16.41224489795918</v>
+        <v>16.35495319795918</v>
       </c>
       <c r="O2">
-        <v>4.841612244897959</v>
+        <v>4.824711193397959</v>
       </c>
       <c r="P2">
-        <v>11.57063265306122</v>
+        <v>11.53024200456122</v>
       </c>
       <c r="Q2">
-        <v>15.77063265306122</v>
+        <v>15.73024200456122</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09581320790900248</v>
+        <v>0.09616936257138477</v>
       </c>
       <c r="T2">
-        <v>0.7736884202461266</v>
+        <v>0.7791980196024247</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>286.4681079102066</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09556228394567091</v>
+        <v>0.09531135998233937</v>
       </c>
       <c r="C3">
-        <v>102.1750278862724</v>
+        <v>101.5066833701198</v>
       </c>
       <c r="D3">
-        <v>100.3740278862724</v>
+        <v>100.8446833701198</v>
       </c>
       <c r="E3">
-        <v>-46.461</v>
+        <v>-45.322</v>
       </c>
       <c r="F3">
-        <v>1.139</v>
+        <v>2.278</v>
       </c>
       <c r="G3">
         <v>2.94</v>
@@ -1533,28 +1533,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M3">
-        <v>0.0572917</v>
+        <v>0.1145834</v>
       </c>
       <c r="N3">
-        <v>16.35495319795918</v>
+        <v>16.29766149795918</v>
       </c>
       <c r="O3">
-        <v>4.824711193397959</v>
+        <v>4.807810141897959</v>
       </c>
       <c r="P3">
-        <v>11.53024200456122</v>
+        <v>11.48985135606122</v>
       </c>
       <c r="Q3">
-        <v>15.73024200456122</v>
+        <v>15.68985135606122</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09616936257138477</v>
+        <v>0.09653278569626467</v>
       </c>
       <c r="T3">
-        <v>0.7791980196024247</v>
+        <v>0.7848200597619127</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>286.4681079102066</v>
+        <v>143.2340539551033</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09531135998233937</v>
+        <v>0.09506043601900781</v>
       </c>
       <c r="C4">
-        <v>101.5066833701198</v>
+        <v>100.8427734707204</v>
       </c>
       <c r="D4">
-        <v>100.8446833701198</v>
+        <v>101.3197734707204</v>
       </c>
       <c r="E4">
-        <v>-45.322</v>
+        <v>-44.183</v>
       </c>
       <c r="F4">
-        <v>2.278</v>
+        <v>3.417</v>
       </c>
       <c r="G4">
         <v>2.94</v>
@@ -1615,28 +1615,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M4">
-        <v>0.1145834</v>
+        <v>0.1718751</v>
       </c>
       <c r="N4">
-        <v>16.29766149795918</v>
+        <v>16.24036979795918</v>
       </c>
       <c r="O4">
-        <v>4.807810141897959</v>
+        <v>4.790909090397959</v>
       </c>
       <c r="P4">
-        <v>11.48985135606122</v>
+        <v>11.44946070756122</v>
       </c>
       <c r="Q4">
-        <v>15.68985135606122</v>
+        <v>15.64946070756122</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09653278569626467</v>
+        <v>0.09690370208145135</v>
       </c>
       <c r="T4">
-        <v>0.7848200597619127</v>
+        <v>0.7905580182752046</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>143.2340539551033</v>
+        <v>95.4893693034022</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09506043601900781</v>
+        <v>0.09480951205567624</v>
       </c>
       <c r="C5">
-        <v>100.8427734707204</v>
+        <v>100.1833611606074</v>
       </c>
       <c r="D5">
-        <v>101.3197734707204</v>
+        <v>101.7993611606074</v>
       </c>
       <c r="E5">
-        <v>-44.183</v>
+        <v>-43.044</v>
       </c>
       <c r="F5">
-        <v>3.417</v>
+        <v>4.556</v>
       </c>
       <c r="G5">
         <v>2.94</v>
@@ -1697,28 +1697,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M5">
-        <v>0.1718751</v>
+        <v>0.2291668</v>
       </c>
       <c r="N5">
-        <v>16.24036979795918</v>
+        <v>16.18307809795918</v>
       </c>
       <c r="O5">
-        <v>4.790909090397959</v>
+        <v>4.774008038897959</v>
       </c>
       <c r="P5">
-        <v>11.44946070756122</v>
+        <v>11.40907005906122</v>
       </c>
       <c r="Q5">
-        <v>15.64946070756122</v>
+        <v>15.60907005906122</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09690370208145135</v>
+        <v>0.09728234589132942</v>
       </c>
       <c r="T5">
-        <v>0.7905580182752046</v>
+        <v>0.7964155175908565</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>95.4893693034022</v>
+        <v>71.61702697755165</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09480951205567624</v>
+        <v>0.09455858809234469</v>
       </c>
       <c r="C6">
-        <v>100.1833611606074</v>
+        <v>99.52851061028318</v>
       </c>
       <c r="D6">
-        <v>101.7993611606074</v>
+        <v>102.2835106102832</v>
       </c>
       <c r="E6">
-        <v>-43.044</v>
+        <v>-41.905</v>
       </c>
       <c r="F6">
-        <v>4.556</v>
+        <v>5.695</v>
       </c>
       <c r="G6">
         <v>2.94</v>
@@ -1779,28 +1779,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M6">
-        <v>0.2291668</v>
+        <v>0.2864585</v>
       </c>
       <c r="N6">
-        <v>16.18307809795918</v>
+        <v>16.12578639795919</v>
       </c>
       <c r="O6">
-        <v>4.774008038897959</v>
+        <v>4.757106987397959</v>
       </c>
       <c r="P6">
-        <v>11.40907005906122</v>
+        <v>11.36867941056123</v>
       </c>
       <c r="Q6">
-        <v>15.60907005906122</v>
+        <v>15.56867941056123</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09728234589132942</v>
+        <v>0.09766896114983652</v>
       </c>
       <c r="T6">
-        <v>0.7964155175908565</v>
+        <v>0.802396332681575</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>71.61702697755165</v>
+        <v>57.29362158204133</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09455858809234469</v>
+        <v>0.09430766412901313</v>
       </c>
       <c r="C7">
-        <v>99.52851061028318</v>
+        <v>98.87828721684214</v>
       </c>
       <c r="D7">
-        <v>102.2835106102832</v>
+        <v>102.7722872168421</v>
       </c>
       <c r="E7">
-        <v>-41.905</v>
+        <v>-40.766</v>
       </c>
       <c r="F7">
-        <v>5.695</v>
+        <v>6.834000000000001</v>
       </c>
       <c r="G7">
         <v>2.94</v>
@@ -1861,28 +1861,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M7">
-        <v>0.2864585</v>
+        <v>0.3437502</v>
       </c>
       <c r="N7">
-        <v>16.12578639795919</v>
+        <v>16.06849469795918</v>
       </c>
       <c r="O7">
-        <v>4.757106987397959</v>
+        <v>4.74020593589796</v>
       </c>
       <c r="P7">
-        <v>11.36867941056123</v>
+        <v>11.32828876206123</v>
       </c>
       <c r="Q7">
-        <v>15.56867941056123</v>
+        <v>15.52828876206122</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09766896114983652</v>
+        <v>0.09806380226490759</v>
       </c>
       <c r="T7">
-        <v>0.802396332681575</v>
+        <v>0.8085043991572023</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.29362158204133</v>
+        <v>47.74468465170111</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09430766412901313</v>
+        <v>0.09405674016568158</v>
       </c>
       <c r="C8">
-        <v>98.87828721684214</v>
+        <v>98.23275763341904</v>
       </c>
       <c r="D8">
-        <v>102.7722872168421</v>
+        <v>103.265757633419</v>
       </c>
       <c r="E8">
-        <v>-40.766</v>
+        <v>-39.627</v>
       </c>
       <c r="F8">
-        <v>6.834000000000001</v>
+        <v>7.973</v>
       </c>
       <c r="G8">
         <v>2.94</v>
@@ -1943,28 +1943,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M8">
-        <v>0.3437502</v>
+        <v>0.4010419</v>
       </c>
       <c r="N8">
-        <v>16.06849469795918</v>
+        <v>16.01120299795918</v>
       </c>
       <c r="O8">
-        <v>4.74020593589796</v>
+        <v>4.723304884397959</v>
       </c>
       <c r="P8">
-        <v>11.32828876206123</v>
+        <v>11.28789811356123</v>
       </c>
       <c r="Q8">
-        <v>15.52828876206122</v>
+        <v>15.48789811356123</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09806380226490759</v>
+        <v>0.09846713458675438</v>
       </c>
       <c r="T8">
-        <v>0.8085043991572023</v>
+        <v>0.8147438219011226</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>47.74468465170111</v>
+        <v>40.92401541574381</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09405674016568157</v>
+        <v>0.09380581620235001</v>
       </c>
       <c r="C9">
-        <v>98.23275763341906</v>
+        <v>97.59198979948926</v>
       </c>
       <c r="D9">
-        <v>103.2657576334191</v>
+        <v>103.7639897994893</v>
       </c>
       <c r="E9">
-        <v>-39.627</v>
+        <v>-38.488</v>
       </c>
       <c r="F9">
-        <v>7.973000000000001</v>
+        <v>9.112</v>
       </c>
       <c r="G9">
         <v>2.94</v>
@@ -2025,28 +2025,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M9">
-        <v>0.4010419</v>
+        <v>0.4583336</v>
       </c>
       <c r="N9">
-        <v>16.01120299795918</v>
+        <v>15.95391129795918</v>
       </c>
       <c r="O9">
-        <v>4.723304884397959</v>
+        <v>4.706403832897959</v>
       </c>
       <c r="P9">
-        <v>11.28789811356123</v>
+        <v>11.24750746506123</v>
       </c>
       <c r="Q9">
-        <v>15.48789811356123</v>
+        <v>15.44750746506122</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09846713458675438</v>
+        <v>0.09887923500255436</v>
       </c>
       <c r="T9">
-        <v>0.8147438219011226</v>
+        <v>0.8211188842699108</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.9240154157438</v>
+        <v>35.80851348877582</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09380581620235001</v>
+        <v>0.09355489223901846</v>
       </c>
       <c r="C10">
-        <v>97.59198979948926</v>
+        <v>96.9560529720506</v>
       </c>
       <c r="D10">
-        <v>103.7639897994893</v>
+        <v>104.2670529720506</v>
       </c>
       <c r="E10">
-        <v>-38.488</v>
+        <v>-37.349</v>
       </c>
       <c r="F10">
-        <v>9.112</v>
+        <v>10.251</v>
       </c>
       <c r="G10">
         <v>2.94</v>
@@ -2107,28 +2107,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M10">
-        <v>0.4583336</v>
+        <v>0.5156253</v>
       </c>
       <c r="N10">
-        <v>15.95391129795918</v>
+        <v>15.89661959795918</v>
       </c>
       <c r="O10">
-        <v>4.706403832897959</v>
+        <v>4.689502781397959</v>
       </c>
       <c r="P10">
-        <v>11.24750746506123</v>
+        <v>11.20711681656122</v>
       </c>
       <c r="Q10">
-        <v>15.44750746506122</v>
+        <v>15.40711681656122</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09887923500255436</v>
+        <v>0.09930039257034996</v>
       </c>
       <c r="T10">
-        <v>0.8211188842699108</v>
+        <v>0.8276340578995517</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.80851348877582</v>
+        <v>31.82978976780074</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09355489223901846</v>
+        <v>0.0933039682756869</v>
       </c>
       <c r="C11">
-        <v>96.9560529720506</v>
+        <v>96.32501775771681</v>
       </c>
       <c r="D11">
-        <v>104.2670529720506</v>
+        <v>104.7750177577168</v>
       </c>
       <c r="E11">
-        <v>-37.349</v>
+        <v>-36.21</v>
       </c>
       <c r="F11">
-        <v>10.251</v>
+        <v>11.39</v>
       </c>
       <c r="G11">
         <v>2.94</v>
@@ -2189,28 +2189,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M11">
-        <v>0.5156253</v>
+        <v>0.5729169999999999</v>
       </c>
       <c r="N11">
-        <v>15.89661959795918</v>
+        <v>15.83932789795918</v>
       </c>
       <c r="O11">
-        <v>4.689502781397959</v>
+        <v>4.672601729897959</v>
       </c>
       <c r="P11">
-        <v>11.20711681656122</v>
+        <v>11.16672616806122</v>
       </c>
       <c r="Q11">
-        <v>15.40711681656122</v>
+        <v>15.36672616806122</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09930039257034996</v>
+        <v>0.09973090919520768</v>
       </c>
       <c r="T11">
-        <v>0.8276340578995517</v>
+        <v>0.8342940131654065</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.82978976780074</v>
+        <v>28.64681079102067</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0933039682756869</v>
+        <v>0.09305304431235535</v>
       </c>
       <c r="C12">
-        <v>96.32501775771681</v>
+        <v>95.69895614575343</v>
       </c>
       <c r="D12">
-        <v>104.7750177577168</v>
+        <v>105.2879561457534</v>
       </c>
       <c r="E12">
-        <v>-36.21</v>
+        <v>-35.071</v>
       </c>
       <c r="F12">
-        <v>11.39</v>
+        <v>12.529</v>
       </c>
       <c r="G12">
         <v>2.94</v>
@@ -2271,28 +2271,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M12">
-        <v>0.572917</v>
+        <v>0.6302087</v>
       </c>
       <c r="N12">
-        <v>15.83932789795918</v>
+        <v>15.78203619795918</v>
       </c>
       <c r="O12">
-        <v>4.672601729897959</v>
+        <v>4.655700678397959</v>
       </c>
       <c r="P12">
-        <v>11.16672616806122</v>
+        <v>11.12633551956122</v>
       </c>
       <c r="Q12">
-        <v>15.36672616806122</v>
+        <v>15.32633551956122</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09973090919520768</v>
+        <v>0.1001711003509611</v>
       </c>
       <c r="T12">
-        <v>0.8342940131654065</v>
+        <v>0.841103630347348</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.64681079102066</v>
+        <v>26.04255526456424</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09305304431235535</v>
+        <v>0.09280212034902378</v>
       </c>
       <c r="C13">
-        <v>95.69895614575343</v>
+        <v>95.07794154208899</v>
       </c>
       <c r="D13">
-        <v>105.2879561457534</v>
+        <v>105.805941542089</v>
       </c>
       <c r="E13">
-        <v>-35.071</v>
+        <v>-33.932</v>
       </c>
       <c r="F13">
-        <v>12.529</v>
+        <v>13.668</v>
       </c>
       <c r="G13">
         <v>2.94</v>
@@ -2353,28 +2353,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M13">
-        <v>0.6302087</v>
+        <v>0.6875004</v>
       </c>
       <c r="N13">
-        <v>15.78203619795918</v>
+        <v>15.72474449795918</v>
       </c>
       <c r="O13">
-        <v>4.655700678397959</v>
+        <v>4.638799626897959</v>
       </c>
       <c r="P13">
-        <v>11.12633551956122</v>
+        <v>11.08594487106123</v>
       </c>
       <c r="Q13">
-        <v>15.32633551956122</v>
+        <v>15.28594487106123</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1001711003509611</v>
+        <v>0.1006212958511634</v>
       </c>
       <c r="T13">
-        <v>0.841103630347348</v>
+        <v>0.848068011556152</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.04255526456424</v>
+        <v>23.87234232585055</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09280212034902378</v>
+        <v>0.09255119638569224</v>
       </c>
       <c r="C14">
-        <v>95.07794154208899</v>
+        <v>94.4620488043351</v>
       </c>
       <c r="D14">
-        <v>105.805941542089</v>
+        <v>106.3290488043351</v>
       </c>
       <c r="E14">
-        <v>-33.932</v>
+        <v>-32.793</v>
       </c>
       <c r="F14">
-        <v>13.668</v>
+        <v>14.807</v>
       </c>
       <c r="G14">
         <v>2.94</v>
@@ -2435,28 +2435,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M14">
-        <v>0.6875004</v>
+        <v>0.7447921</v>
       </c>
       <c r="N14">
-        <v>15.72474449795918</v>
+        <v>15.66745279795918</v>
       </c>
       <c r="O14">
-        <v>4.638799626897959</v>
+        <v>4.621898575397959</v>
       </c>
       <c r="P14">
-        <v>11.08594487106123</v>
+        <v>11.04555422256123</v>
       </c>
       <c r="Q14">
-        <v>15.28594487106123</v>
+        <v>15.24555422256122</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1006212958511634</v>
+        <v>0.1010818406732095</v>
       </c>
       <c r="T14">
-        <v>0.848068011556152</v>
+        <v>0.8551924934823997</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.87234232585055</v>
+        <v>22.03600830078512</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09255119638569224</v>
+        <v>0.09230027242236068</v>
       </c>
       <c r="C15">
-        <v>94.4620488043351</v>
+        <v>93.85135427785067</v>
       </c>
       <c r="D15">
-        <v>106.3290488043351</v>
+        <v>106.8573542778507</v>
       </c>
       <c r="E15">
-        <v>-32.793</v>
+        <v>-31.654</v>
       </c>
       <c r="F15">
-        <v>14.807</v>
+        <v>15.946</v>
       </c>
       <c r="G15">
         <v>2.94</v>
@@ -2517,28 +2517,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M15">
-        <v>0.7447921</v>
+        <v>0.8020838</v>
       </c>
       <c r="N15">
-        <v>15.66745279795918</v>
+        <v>15.61016109795918</v>
       </c>
       <c r="O15">
-        <v>4.621898575397959</v>
+        <v>4.604997523897959</v>
       </c>
       <c r="P15">
-        <v>11.04555422256123</v>
+        <v>11.00516357406122</v>
       </c>
       <c r="Q15">
-        <v>15.24555422256122</v>
+        <v>15.20516357406122</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1010818406732095</v>
+        <v>0.1015530958399543</v>
       </c>
       <c r="T15">
-        <v>0.8551924934823997</v>
+        <v>0.8624826610348391</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.03600830078512</v>
+        <v>20.4620077078719</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09230027242236068</v>
+        <v>0.09204934845902912</v>
       </c>
       <c r="C16">
-        <v>93.85135427785067</v>
+        <v>93.24593583288623</v>
       </c>
       <c r="D16">
-        <v>106.8573542778507</v>
+        <v>107.3909358328862</v>
       </c>
       <c r="E16">
-        <v>-31.654</v>
+        <v>-30.515</v>
       </c>
       <c r="F16">
-        <v>15.946</v>
+        <v>17.085</v>
       </c>
       <c r="G16">
         <v>2.94</v>
@@ -2599,28 +2599,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M16">
-        <v>0.8020838</v>
+        <v>0.8593755000000002</v>
       </c>
       <c r="N16">
-        <v>15.61016109795918</v>
+        <v>15.55286939795918</v>
       </c>
       <c r="O16">
-        <v>4.604997523897959</v>
+        <v>4.588096472397959</v>
       </c>
       <c r="P16">
-        <v>11.00516357406122</v>
+        <v>10.96477292556122</v>
       </c>
       <c r="Q16">
-        <v>15.20516357406122</v>
+        <v>15.16477292556122</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1015530958399543</v>
+        <v>0.1020354393635637</v>
       </c>
       <c r="T16">
-        <v>0.8624826610348391</v>
+        <v>0.8699443619414536</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.4620077078719</v>
+        <v>19.09787386068044</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09204934845902912</v>
+        <v>0.09179842449569756</v>
       </c>
       <c r="C17">
-        <v>93.24593583288623</v>
+        <v>92.6458729028473</v>
       </c>
       <c r="D17">
-        <v>107.3909358328862</v>
+        <v>107.9298729028473</v>
       </c>
       <c r="E17">
-        <v>-30.515</v>
+        <v>-29.376</v>
       </c>
       <c r="F17">
-        <v>17.085</v>
+        <v>18.224</v>
       </c>
       <c r="G17">
         <v>2.94</v>
@@ -2681,28 +2681,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M17">
-        <v>0.8593755</v>
+        <v>0.9166672</v>
       </c>
       <c r="N17">
-        <v>15.55286939795918</v>
+        <v>15.49557769795918</v>
       </c>
       <c r="O17">
-        <v>4.588096472397959</v>
+        <v>4.571195420897959</v>
       </c>
       <c r="P17">
-        <v>10.96477292556122</v>
+        <v>10.92438227706123</v>
       </c>
       <c r="Q17">
-        <v>15.16477292556122</v>
+        <v>15.12438227706122</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1020354393635637</v>
+        <v>0.1025292672567828</v>
       </c>
       <c r="T17">
-        <v>0.8699443619414536</v>
+        <v>0.8775837223934636</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.09787386068044</v>
+        <v>17.90425674438792</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09179842449569756</v>
+        <v>0.091547500532366</v>
       </c>
       <c r="C18">
-        <v>92.6458729028473</v>
+        <v>92.05124652371502</v>
       </c>
       <c r="D18">
-        <v>107.9298729028473</v>
+        <v>108.474246523715</v>
       </c>
       <c r="E18">
-        <v>-29.376</v>
+        <v>-28.237</v>
       </c>
       <c r="F18">
-        <v>18.224</v>
+        <v>19.363</v>
       </c>
       <c r="G18">
         <v>2.94</v>
@@ -2763,28 +2763,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M18">
-        <v>0.9166672</v>
+        <v>0.9739589000000001</v>
       </c>
       <c r="N18">
-        <v>15.49557769795918</v>
+        <v>15.43828599795918</v>
       </c>
       <c r="O18">
-        <v>4.571195420897959</v>
+        <v>4.554294369397959</v>
       </c>
       <c r="P18">
-        <v>10.92438227706123</v>
+        <v>10.88399162856123</v>
       </c>
       <c r="Q18">
-        <v>15.12438227706122</v>
+        <v>15.08399162856123</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1025292672567828</v>
+        <v>0.1030349946173084</v>
       </c>
       <c r="T18">
-        <v>0.8775837223934636</v>
+        <v>0.885407163820221</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.90425674438792</v>
+        <v>16.85106517118862</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.091547500532366</v>
+        <v>0.09129657656903445</v>
       </c>
       <c r="C19">
-        <v>92.05124652371502</v>
+        <v>91.46213937466646</v>
       </c>
       <c r="D19">
-        <v>108.474246523715</v>
+        <v>109.0241393746665</v>
       </c>
       <c r="E19">
-        <v>-28.237</v>
+        <v>-27.098</v>
       </c>
       <c r="F19">
-        <v>19.363</v>
+        <v>20.502</v>
       </c>
       <c r="G19">
         <v>2.94</v>
@@ -2845,28 +2845,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M19">
-        <v>0.9739589000000001</v>
+        <v>1.0312506</v>
       </c>
       <c r="N19">
-        <v>15.43828599795918</v>
+        <v>15.38099429795918</v>
       </c>
       <c r="O19">
-        <v>4.554294369397959</v>
+        <v>4.537393317897959</v>
       </c>
       <c r="P19">
-        <v>10.88399162856123</v>
+        <v>10.84360098006123</v>
       </c>
       <c r="Q19">
-        <v>15.08399162856123</v>
+        <v>15.04360098006122</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1030349946173084</v>
+        <v>0.1035530567915054</v>
       </c>
       <c r="T19">
-        <v>0.885407163820221</v>
+        <v>0.8934214208915333</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.85106517118862</v>
+        <v>15.91489488390036</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09129657656903446</v>
+        <v>0.09104565260570291</v>
       </c>
       <c r="C20">
-        <v>91.46213937466644</v>
+        <v>90.87863581993626</v>
       </c>
       <c r="D20">
-        <v>109.0241393746664</v>
+        <v>109.5796358199363</v>
       </c>
       <c r="E20">
-        <v>-27.098</v>
+        <v>-25.959</v>
       </c>
       <c r="F20">
-        <v>20.502</v>
+        <v>21.641</v>
       </c>
       <c r="G20">
         <v>2.94</v>
@@ -2927,28 +2927,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M20">
-        <v>1.0312506</v>
+        <v>1.0885423</v>
       </c>
       <c r="N20">
-        <v>15.38099429795918</v>
+        <v>15.32370259795918</v>
       </c>
       <c r="O20">
-        <v>4.537393317897959</v>
+        <v>4.520492266397959</v>
       </c>
       <c r="P20">
-        <v>10.84360098006123</v>
+        <v>10.80321033156122</v>
       </c>
       <c r="Q20">
-        <v>15.04360098006122</v>
+        <v>15.00321033156122</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1035530567915054</v>
+        <v>0.1040839106243246</v>
       </c>
       <c r="T20">
-        <v>0.8934214208915333</v>
+        <v>0.9016335608534953</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.91489488390037</v>
+        <v>15.07726883737929</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09104565260570291</v>
+        <v>0.09079472864237134</v>
       </c>
       <c r="C21">
-        <v>90.87863581993626</v>
+        <v>90.30082195196486</v>
       </c>
       <c r="D21">
-        <v>109.5796358199363</v>
+        <v>110.1408219519649</v>
       </c>
       <c r="E21">
-        <v>-25.959</v>
+        <v>-24.82</v>
       </c>
       <c r="F21">
-        <v>21.641</v>
+        <v>22.78</v>
       </c>
       <c r="G21">
         <v>2.94</v>
@@ -3009,28 +3009,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M21">
-        <v>1.0885423</v>
+        <v>1.145834</v>
       </c>
       <c r="N21">
-        <v>15.32370259795918</v>
+        <v>15.26641089795918</v>
       </c>
       <c r="O21">
-        <v>4.520492266397959</v>
+        <v>4.503591214897959</v>
       </c>
       <c r="P21">
-        <v>10.80321033156122</v>
+        <v>10.76281968306122</v>
       </c>
       <c r="Q21">
-        <v>15.00321033156122</v>
+        <v>14.96281968306122</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1040839106243246</v>
+        <v>0.1046280358029642</v>
       </c>
       <c r="T21">
-        <v>0.9016335608534953</v>
+        <v>0.9100510043145065</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.07726883737929</v>
+        <v>14.32340539551033</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09079472864237134</v>
+        <v>0.09054380467903977</v>
       </c>
       <c r="C22">
-        <v>90.30082195196486</v>
+        <v>89.72878563587909</v>
       </c>
       <c r="D22">
-        <v>110.1408219519649</v>
+        <v>110.7077856358791</v>
       </c>
       <c r="E22">
-        <v>-24.82</v>
+        <v>-23.681</v>
       </c>
       <c r="F22">
-        <v>22.78</v>
+        <v>23.919</v>
       </c>
       <c r="G22">
         <v>2.94</v>
@@ -3091,28 +3091,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M22">
-        <v>1.145834</v>
+        <v>1.2031257</v>
       </c>
       <c r="N22">
-        <v>15.26641089795918</v>
+        <v>15.20911919795918</v>
       </c>
       <c r="O22">
-        <v>4.503591214897959</v>
+        <v>4.486690163397959</v>
       </c>
       <c r="P22">
-        <v>10.76281968306122</v>
+        <v>10.72242903456122</v>
       </c>
       <c r="Q22">
-        <v>14.96281968306122</v>
+        <v>14.92242903456122</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1046280358029642</v>
+        <v>0.105185936302582</v>
       </c>
       <c r="T22">
-        <v>0.9100510043145065</v>
+        <v>0.9186815476099736</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.32340539551033</v>
+        <v>13.6413384719146</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09054380467903977</v>
+        <v>0.09029288071570823</v>
       </c>
       <c r="C23">
-        <v>89.72878563587911</v>
+        <v>89.16261655535399</v>
       </c>
       <c r="D23">
-        <v>110.7077856358791</v>
+        <v>111.280616555354</v>
       </c>
       <c r="E23">
-        <v>-23.681</v>
+        <v>-22.542</v>
       </c>
       <c r="F23">
-        <v>23.919</v>
+        <v>25.058</v>
       </c>
       <c r="G23">
         <v>2.94</v>
@@ -3173,28 +3173,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M23">
-        <v>1.2031257</v>
+        <v>1.2604174</v>
       </c>
       <c r="N23">
-        <v>15.20911919795918</v>
+        <v>15.15182749795918</v>
       </c>
       <c r="O23">
-        <v>4.486690163397959</v>
+        <v>4.469789111897959</v>
       </c>
       <c r="P23">
-        <v>10.72242903456122</v>
+        <v>10.68203838606123</v>
       </c>
       <c r="Q23">
-        <v>14.92242903456122</v>
+        <v>14.88203838606123</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.105185936302582</v>
+        <v>0.1057581419432157</v>
       </c>
       <c r="T23">
-        <v>0.9186815476099736</v>
+        <v>0.9275333868873756</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.6413384719146</v>
+        <v>13.02127763228212</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09029288071570823</v>
+        <v>0.09028518175237667</v>
       </c>
       <c r="C24">
-        <v>89.16261655535399</v>
+        <v>88.04128616181607</v>
       </c>
       <c r="D24">
-        <v>111.280616555354</v>
+        <v>111.2982861618161</v>
       </c>
       <c r="E24">
-        <v>-22.542</v>
+        <v>-21.403</v>
       </c>
       <c r="F24">
-        <v>25.058</v>
+        <v>26.197</v>
       </c>
       <c r="G24">
         <v>2.94</v>
@@ -3255,45 +3255,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M24">
-        <v>1.2604174</v>
+        <v>1.3570046</v>
       </c>
       <c r="N24">
-        <v>15.15182749795918</v>
+        <v>15.05524029795918</v>
       </c>
       <c r="O24">
-        <v>4.469789111897959</v>
+        <v>4.441295887897959</v>
       </c>
       <c r="P24">
-        <v>10.68203838606123</v>
+        <v>10.61394441006123</v>
       </c>
       <c r="Q24">
-        <v>14.88203838606123</v>
+        <v>14.81394441006123</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1057581419432157</v>
+        <v>0.1063452100680216</v>
       </c>
       <c r="T24">
-        <v>0.9275333868873756</v>
+        <v>0.936615144068087</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.295</v>
       </c>
       <c r="W24">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.02127763228212</v>
+        <v>12.09446519043427</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09028518175237667</v>
+        <v>0.09004483278904511</v>
       </c>
       <c r="C25">
-        <v>88.04128616181607</v>
+        <v>87.45673818953287</v>
       </c>
       <c r="D25">
-        <v>111.2982861618161</v>
+        <v>111.8527381895329</v>
       </c>
       <c r="E25">
-        <v>-21.403</v>
+        <v>-20.264</v>
       </c>
       <c r="F25">
-        <v>26.197</v>
+        <v>27.336</v>
       </c>
       <c r="G25">
         <v>2.94</v>
@@ -3337,28 +3337,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M25">
-        <v>1.3570046</v>
+        <v>1.4160048</v>
       </c>
       <c r="N25">
-        <v>15.05524029795918</v>
+        <v>14.99624009795918</v>
       </c>
       <c r="O25">
-        <v>4.441295887897959</v>
+        <v>4.423890828897959</v>
       </c>
       <c r="P25">
-        <v>10.61394441006123</v>
+        <v>10.57234926906122</v>
       </c>
       <c r="Q25">
-        <v>14.81394441006123</v>
+        <v>14.77234926906122</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1063452100680216</v>
+        <v>0.1069477273540067</v>
       </c>
       <c r="T25">
-        <v>0.936615144068087</v>
+        <v>0.945935894858817</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.09446519043427</v>
+        <v>11.59052914083284</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09004483278904511</v>
+        <v>0.08980448382571356</v>
       </c>
       <c r="C26">
-        <v>87.45673818953287</v>
+        <v>86.87774207579673</v>
       </c>
       <c r="D26">
-        <v>111.8527381895329</v>
+        <v>112.4127420757967</v>
       </c>
       <c r="E26">
-        <v>-20.264</v>
+        <v>-19.125</v>
       </c>
       <c r="F26">
-        <v>27.336</v>
+        <v>28.475</v>
       </c>
       <c r="G26">
         <v>2.94</v>
@@ -3419,28 +3419,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M26">
-        <v>1.4160048</v>
+        <v>1.475005</v>
       </c>
       <c r="N26">
-        <v>14.99624009795918</v>
+        <v>14.93723989795918</v>
       </c>
       <c r="O26">
-        <v>4.423890828897959</v>
+        <v>4.406485769897959</v>
       </c>
       <c r="P26">
-        <v>10.57234926906122</v>
+        <v>10.53075412806123</v>
       </c>
       <c r="Q26">
-        <v>14.77234926906122</v>
+        <v>14.73075412806122</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1069477273540067</v>
+        <v>0.1075663117676181</v>
       </c>
       <c r="T26">
-        <v>0.945935894858817</v>
+        <v>0.9555051990039665</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.59052914083284</v>
+        <v>11.12690797519953</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08980448382571356</v>
+        <v>0.08956413486238199</v>
       </c>
       <c r="C27">
-        <v>86.87774207579673</v>
+        <v>86.30438162829878</v>
       </c>
       <c r="D27">
-        <v>112.4127420757967</v>
+        <v>112.9783816282988</v>
       </c>
       <c r="E27">
-        <v>-19.125</v>
+        <v>-17.986</v>
       </c>
       <c r="F27">
-        <v>28.475</v>
+        <v>29.614</v>
       </c>
       <c r="G27">
         <v>2.94</v>
@@ -3501,28 +3501,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M27">
-        <v>1.475005</v>
+        <v>1.5340052</v>
       </c>
       <c r="N27">
-        <v>14.93723989795918</v>
+        <v>14.87823969795918</v>
       </c>
       <c r="O27">
-        <v>4.406485769897959</v>
+        <v>4.389080710897959</v>
       </c>
       <c r="P27">
-        <v>10.53075412806123</v>
+        <v>10.48915898706123</v>
       </c>
       <c r="Q27">
-        <v>14.73075412806122</v>
+        <v>14.68915898706122</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1075663117676181</v>
+        <v>0.1082016146788946</v>
       </c>
       <c r="T27">
-        <v>0.9555051990039665</v>
+        <v>0.9653331329908766</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.12690797519953</v>
+        <v>10.6989499761534</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08956413486238199</v>
+        <v>0.08932378589905043</v>
       </c>
       <c r="C28">
-        <v>86.30438162829878</v>
+        <v>85.73674235007809</v>
       </c>
       <c r="D28">
-        <v>112.9783816282988</v>
+        <v>113.5497423500781</v>
       </c>
       <c r="E28">
-        <v>-17.986</v>
+        <v>-16.847</v>
       </c>
       <c r="F28">
-        <v>29.614</v>
+        <v>30.753</v>
       </c>
       <c r="G28">
         <v>2.94</v>
@@ -3583,28 +3583,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M28">
-        <v>1.5340052</v>
+        <v>1.5930054</v>
       </c>
       <c r="N28">
-        <v>14.87823969795918</v>
+        <v>14.81923949795918</v>
       </c>
       <c r="O28">
-        <v>4.389080710897959</v>
+        <v>4.371675651897958</v>
       </c>
       <c r="P28">
-        <v>10.48915898706123</v>
+        <v>10.44756384606123</v>
       </c>
       <c r="Q28">
-        <v>14.68915898706122</v>
+        <v>14.64756384606122</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1082016146788946</v>
+        <v>0.1088543231493841</v>
       </c>
       <c r="T28">
-        <v>0.9653331329908766</v>
+        <v>0.9754303254431816</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.6989499761534</v>
+        <v>10.30269256962919</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08932378589905043</v>
+        <v>0.08908343693571887</v>
       </c>
       <c r="C29">
-        <v>85.73674235007809</v>
+        <v>85.17491148260899</v>
       </c>
       <c r="D29">
-        <v>113.5497423500781</v>
+        <v>114.126911482609</v>
       </c>
       <c r="E29">
-        <v>-16.847</v>
+        <v>-15.708</v>
       </c>
       <c r="F29">
-        <v>30.753</v>
+        <v>31.892</v>
       </c>
       <c r="G29">
         <v>2.94</v>
@@ -3665,28 +3665,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M29">
-        <v>1.5930054</v>
+        <v>1.6520056</v>
       </c>
       <c r="N29">
-        <v>14.81923949795918</v>
+        <v>14.76023929795918</v>
       </c>
       <c r="O29">
-        <v>4.371675651897958</v>
+        <v>4.354270592897959</v>
       </c>
       <c r="P29">
-        <v>10.44756384606123</v>
+        <v>10.40596870506122</v>
       </c>
       <c r="Q29">
-        <v>14.64756384606122</v>
+        <v>14.60596870506122</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1088543231493841</v>
+        <v>0.1095251624107207</v>
       </c>
       <c r="T29">
-        <v>0.9754303254431816</v>
+        <v>0.9858079954636063</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.30269256962919</v>
+        <v>9.934739263571009</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08908343693571887</v>
+        <v>0.08919065297238732</v>
       </c>
       <c r="C30">
-        <v>85.17491148260899</v>
+        <v>83.77772179921072</v>
       </c>
       <c r="D30">
-        <v>114.126911482609</v>
+        <v>113.8687217992107</v>
       </c>
       <c r="E30">
-        <v>-15.708</v>
+        <v>-14.569</v>
       </c>
       <c r="F30">
-        <v>31.892</v>
+        <v>33.03100000000001</v>
       </c>
       <c r="G30">
         <v>2.94</v>
@@ -3747,45 +3747,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M30">
-        <v>1.6520056</v>
+        <v>1.7671585</v>
       </c>
       <c r="N30">
-        <v>14.76023929795918</v>
+        <v>14.64508639795918</v>
       </c>
       <c r="O30">
-        <v>4.354270592897959</v>
+        <v>4.320300487397959</v>
       </c>
       <c r="P30">
-        <v>10.40596870506122</v>
+        <v>10.32478591056122</v>
       </c>
       <c r="Q30">
-        <v>14.60596870506122</v>
+        <v>14.52478591056122</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1095251624107207</v>
+        <v>0.1102148985526582</v>
       </c>
       <c r="T30">
-        <v>0.9858079954636063</v>
+        <v>0.9964779942170008</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.295</v>
       </c>
       <c r="W30">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>9.934739263571009</v>
+        <v>9.287364375045691</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08919065297238732</v>
+        <v>0.08896228900905576</v>
       </c>
       <c r="C31">
-        <v>83.77772179921072</v>
+        <v>83.19006348202004</v>
       </c>
       <c r="D31">
-        <v>113.8687217992107</v>
+        <v>114.42006348202</v>
       </c>
       <c r="E31">
-        <v>-14.569</v>
+        <v>-13.43</v>
       </c>
       <c r="F31">
-        <v>33.031</v>
+        <v>34.17</v>
       </c>
       <c r="G31">
         <v>2.94</v>
@@ -3829,28 +3829,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M31">
-        <v>1.7671585</v>
+        <v>1.828095</v>
       </c>
       <c r="N31">
-        <v>14.64508639795918</v>
+        <v>14.58414989795918</v>
       </c>
       <c r="O31">
-        <v>4.320300487397959</v>
+        <v>4.302324219897959</v>
       </c>
       <c r="P31">
-        <v>10.32478591056122</v>
+        <v>10.28182567806122</v>
       </c>
       <c r="Q31">
-        <v>14.52478591056122</v>
+        <v>14.48182567806122</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1102148985526582</v>
+        <v>0.1109243414415082</v>
       </c>
       <c r="T31">
-        <v>0.9964779942170008</v>
+        <v>1.007452850077635</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.287364375045692</v>
+        <v>8.97778556254417</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08896228900905576</v>
+        <v>0.08873392504572421</v>
       </c>
       <c r="C32">
-        <v>83.19006348202004</v>
+        <v>82.60777023152772</v>
       </c>
       <c r="D32">
-        <v>114.42006348202</v>
+        <v>114.9767702315277</v>
       </c>
       <c r="E32">
-        <v>-13.43</v>
+        <v>-12.291</v>
       </c>
       <c r="F32">
-        <v>34.17</v>
+        <v>35.309</v>
       </c>
       <c r="G32">
         <v>2.94</v>
@@ -3911,28 +3911,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M32">
-        <v>1.828095</v>
+        <v>1.8890315</v>
       </c>
       <c r="N32">
-        <v>14.58414989795918</v>
+        <v>14.52321339795918</v>
       </c>
       <c r="O32">
-        <v>4.302324219897959</v>
+        <v>4.284347952397959</v>
       </c>
       <c r="P32">
-        <v>10.28182567806122</v>
+        <v>10.23886544556122</v>
       </c>
       <c r="Q32">
-        <v>14.48182567806122</v>
+        <v>14.43886544556122</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1109243414415082</v>
+        <v>0.1116543478923539</v>
       </c>
       <c r="T32">
-        <v>1.007452850077635</v>
+        <v>1.018745817702345</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.97778556254417</v>
+        <v>8.688179576655648</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08873392504572421</v>
+        <v>0.08850556108239263</v>
       </c>
       <c r="C33">
-        <v>82.60777023152772</v>
+        <v>82.03092074123785</v>
       </c>
       <c r="D33">
-        <v>114.9767702315277</v>
+        <v>115.5389207412378</v>
       </c>
       <c r="E33">
-        <v>-12.291</v>
+        <v>-11.152</v>
       </c>
       <c r="F33">
-        <v>35.309</v>
+        <v>36.448</v>
       </c>
       <c r="G33">
         <v>2.94</v>
@@ -3993,28 +3993,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M33">
-        <v>1.8890315</v>
+        <v>1.949968</v>
       </c>
       <c r="N33">
-        <v>14.52321339795918</v>
+        <v>14.46227689795918</v>
       </c>
       <c r="O33">
-        <v>4.284347952397959</v>
+        <v>4.266371684897959</v>
       </c>
       <c r="P33">
-        <v>10.23886544556122</v>
+        <v>10.19590521306122</v>
       </c>
       <c r="Q33">
-        <v>14.43886544556122</v>
+        <v>14.39590521306122</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1116543478923539</v>
+        <v>0.1124058251211656</v>
       </c>
       <c r="T33">
-        <v>1.018745817702345</v>
+        <v>1.030370931433665</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.688179576655648</v>
+        <v>8.41667396488516</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08850556108239263</v>
+        <v>0.08827719711906107</v>
       </c>
       <c r="C34">
-        <v>82.03092074123785</v>
+        <v>81.45959525122581</v>
       </c>
       <c r="D34">
-        <v>115.5389207412378</v>
+        <v>116.1065952512258</v>
       </c>
       <c r="E34">
-        <v>-11.152</v>
+        <v>-10.013</v>
       </c>
       <c r="F34">
-        <v>36.448</v>
+        <v>37.587</v>
       </c>
       <c r="G34">
         <v>2.94</v>
@@ -4075,28 +4075,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M34">
-        <v>1.949968</v>
+        <v>2.0109045</v>
       </c>
       <c r="N34">
-        <v>14.46227689795918</v>
+        <v>14.40134039795918</v>
       </c>
       <c r="O34">
-        <v>4.266371684897959</v>
+        <v>4.248395417397959</v>
       </c>
       <c r="P34">
-        <v>10.19590521306122</v>
+        <v>10.15294498056122</v>
       </c>
       <c r="Q34">
-        <v>14.39590521306122</v>
+        <v>14.35294498056122</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1124058251211656</v>
+        <v>0.1131797345060613</v>
       </c>
       <c r="T34">
-        <v>1.030370931433665</v>
+        <v>1.042343063485323</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.41667396488516</v>
+        <v>8.161623238676517</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08827719711906107</v>
+        <v>0.08804883315572953</v>
       </c>
       <c r="C35">
-        <v>81.45959525122581</v>
+        <v>80.89387558631961</v>
       </c>
       <c r="D35">
-        <v>116.1065952512258</v>
+        <v>116.6798755863196</v>
       </c>
       <c r="E35">
-        <v>-10.013</v>
+        <v>-8.873999999999995</v>
       </c>
       <c r="F35">
-        <v>37.587</v>
+        <v>38.72600000000001</v>
       </c>
       <c r="G35">
         <v>2.94</v>
@@ -4157,28 +4157,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M35">
-        <v>2.0109045</v>
+        <v>2.071841</v>
       </c>
       <c r="N35">
-        <v>14.40134039795918</v>
+        <v>14.34040389795918</v>
       </c>
       <c r="O35">
-        <v>4.248395417397959</v>
+        <v>4.230419149897958</v>
       </c>
       <c r="P35">
-        <v>10.15294498056122</v>
+        <v>10.10998474806122</v>
       </c>
       <c r="Q35">
-        <v>14.35294498056122</v>
+        <v>14.30998474806122</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1131797345060613</v>
+        <v>0.1139770956904993</v>
       </c>
       <c r="T35">
-        <v>1.042343063485323</v>
+        <v>1.054677987417334</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.161623238676517</v>
+        <v>7.9215754963625</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08804883315572953</v>
+        <v>0.08782046919239797</v>
       </c>
       <c r="C36">
-        <v>80.89387558631961</v>
+        <v>80.33384519541802</v>
       </c>
       <c r="D36">
-        <v>116.6798755863196</v>
+        <v>117.258845195418</v>
       </c>
       <c r="E36">
-        <v>-8.873999999999995</v>
+        <v>-7.734999999999992</v>
       </c>
       <c r="F36">
-        <v>38.72600000000001</v>
+        <v>39.86500000000001</v>
       </c>
       <c r="G36">
         <v>2.94</v>
@@ -4239,28 +4239,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M36">
-        <v>2.071841</v>
+        <v>2.1327775</v>
       </c>
       <c r="N36">
-        <v>14.34040389795918</v>
+        <v>14.27946739795918</v>
       </c>
       <c r="O36">
-        <v>4.230419149897958</v>
+        <v>4.212442882397959</v>
       </c>
       <c r="P36">
-        <v>10.10998474806122</v>
+        <v>10.06702451556123</v>
       </c>
       <c r="Q36">
-        <v>14.30998474806122</v>
+        <v>14.26702451556122</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1139770956904993</v>
+        <v>0.1147989910652276</v>
       </c>
       <c r="T36">
-        <v>1.054677987417334</v>
+        <v>1.067392447470329</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.9215754963625</v>
+        <v>7.695244767895002</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08782046919239797</v>
+        <v>0.08779514522906641</v>
       </c>
       <c r="C37">
-        <v>80.33384519541802</v>
+        <v>79.25940297218003</v>
       </c>
       <c r="D37">
-        <v>117.258845195418</v>
+        <v>117.32340297218</v>
       </c>
       <c r="E37">
-        <v>-7.734999999999992</v>
+        <v>-6.595999999999997</v>
       </c>
       <c r="F37">
-        <v>39.86500000000001</v>
+        <v>41.004</v>
       </c>
       <c r="G37">
         <v>2.94</v>
@@ -4321,45 +4321,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M37">
-        <v>2.1327775</v>
+        <v>2.2265172</v>
       </c>
       <c r="N37">
-        <v>14.27946739795918</v>
+        <v>14.18572769795918</v>
       </c>
       <c r="O37">
-        <v>4.212442882397959</v>
+        <v>4.184789670897959</v>
       </c>
       <c r="P37">
-        <v>10.06702451556123</v>
+        <v>10.00093802706122</v>
       </c>
       <c r="Q37">
-        <v>14.26702451556122</v>
+        <v>14.20093802706122</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1147989910652276</v>
+        <v>0.1156465706704163</v>
       </c>
       <c r="T37">
-        <v>1.067392447470329</v>
+        <v>1.080504234399981</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.295</v>
       </c>
       <c r="W37">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.695244767895002</v>
+        <v>7.37126346832586</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08779514522906642</v>
+        <v>0.08757242126573485</v>
       </c>
       <c r="C38">
-        <v>79.25940297217997</v>
+        <v>78.6912646651562</v>
       </c>
       <c r="D38">
-        <v>117.32340297218</v>
+        <v>117.8942646651562</v>
       </c>
       <c r="E38">
-        <v>-6.596000000000004</v>
+        <v>-5.457000000000001</v>
       </c>
       <c r="F38">
-        <v>41.004</v>
+        <v>42.143</v>
       </c>
       <c r="G38">
         <v>2.94</v>
@@ -4403,28 +4403,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M38">
-        <v>2.2265172</v>
+        <v>2.2883649</v>
       </c>
       <c r="N38">
-        <v>14.18572769795918</v>
+        <v>14.12387999795918</v>
       </c>
       <c r="O38">
-        <v>4.184789670897959</v>
+        <v>4.166544599397959</v>
       </c>
       <c r="P38">
-        <v>10.00093802706122</v>
+        <v>9.957335398561225</v>
       </c>
       <c r="Q38">
-        <v>14.20093802706122</v>
+        <v>14.15733539856122</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1156465706704163</v>
+        <v>0.1165210575646585</v>
       </c>
       <c r="T38">
-        <v>1.080504234399981</v>
+        <v>1.094032268533749</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.371263468325861</v>
+        <v>7.172040131344081</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08757242126573485</v>
+        <v>0.0873496973024033</v>
       </c>
       <c r="C39">
-        <v>78.6912646651562</v>
+        <v>78.12870881602038</v>
       </c>
       <c r="D39">
-        <v>117.8942646651562</v>
+        <v>118.4707088160204</v>
       </c>
       <c r="E39">
-        <v>-5.457000000000001</v>
+        <v>-4.317999999999998</v>
       </c>
       <c r="F39">
-        <v>42.143</v>
+        <v>43.282</v>
       </c>
       <c r="G39">
         <v>2.94</v>
@@ -4485,28 +4485,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M39">
-        <v>2.2883649</v>
+        <v>2.3502126</v>
       </c>
       <c r="N39">
-        <v>14.12387999795918</v>
+        <v>14.06203229795918</v>
       </c>
       <c r="O39">
-        <v>4.166544599397959</v>
+        <v>4.148299527897959</v>
       </c>
       <c r="P39">
-        <v>9.957335398561225</v>
+        <v>9.913732770061223</v>
       </c>
       <c r="Q39">
-        <v>14.15733539856122</v>
+        <v>14.11373277006122</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1165210575646585</v>
+        <v>0.1174237537135537</v>
       </c>
       <c r="T39">
-        <v>1.094032268533749</v>
+        <v>1.10799669086538</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.172040131344081</v>
+        <v>6.983302233150814</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0873496973024033</v>
+        <v>0.08712697333907175</v>
       </c>
       <c r="C40">
-        <v>78.12870881602038</v>
+        <v>77.57181771342708</v>
       </c>
       <c r="D40">
-        <v>118.4707088160204</v>
+        <v>119.0528177134271</v>
       </c>
       <c r="E40">
-        <v>-4.317999999999998</v>
+        <v>-3.178999999999995</v>
       </c>
       <c r="F40">
-        <v>43.282</v>
+        <v>44.42100000000001</v>
       </c>
       <c r="G40">
         <v>2.94</v>
@@ -4567,28 +4567,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M40">
-        <v>2.3502126</v>
+        <v>2.4120603</v>
       </c>
       <c r="N40">
-        <v>14.06203229795918</v>
+        <v>14.00018459795918</v>
       </c>
       <c r="O40">
-        <v>4.148299527897959</v>
+        <v>4.130054456397959</v>
       </c>
       <c r="P40">
-        <v>9.913732770061223</v>
+        <v>9.870130141561225</v>
       </c>
       <c r="Q40">
-        <v>14.11373277006122</v>
+        <v>14.07013014156122</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1174237537135537</v>
+        <v>0.1183560464574947</v>
       </c>
       <c r="T40">
-        <v>1.10799669086538</v>
+        <v>1.122418963109524</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.983302233150814</v>
+        <v>6.804243201531563</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08712697333907175</v>
+        <v>0.08690424937574021</v>
       </c>
       <c r="C41">
-        <v>77.57181771342708</v>
+        <v>77.0206752713264</v>
       </c>
       <c r="D41">
-        <v>119.0528177134271</v>
+        <v>119.6406752713264</v>
       </c>
       <c r="E41">
-        <v>-3.178999999999995</v>
+        <v>-2.039999999999999</v>
       </c>
       <c r="F41">
-        <v>44.42100000000001</v>
+        <v>45.56</v>
       </c>
       <c r="G41">
         <v>2.94</v>
@@ -4649,28 +4649,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M41">
-        <v>2.4120603</v>
+        <v>2.473908</v>
       </c>
       <c r="N41">
-        <v>14.00018459795918</v>
+        <v>13.93833689795918</v>
       </c>
       <c r="O41">
-        <v>4.130054456397959</v>
+        <v>4.111809384897959</v>
       </c>
       <c r="P41">
-        <v>9.870130141561225</v>
+        <v>9.826527513061226</v>
       </c>
       <c r="Q41">
-        <v>14.07013014156122</v>
+        <v>14.02652751306123</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1183560464574947</v>
+        <v>0.1193194156262337</v>
       </c>
       <c r="T41">
-        <v>1.122418963109524</v>
+        <v>1.137321977761806</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.804243201531563</v>
+        <v>6.634137121493274</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08690424937574021</v>
+        <v>0.08668152541240862</v>
       </c>
       <c r="C42">
-        <v>77.0206752713264</v>
+        <v>76.47536706929012</v>
       </c>
       <c r="D42">
-        <v>119.6406752713264</v>
+        <v>120.2343670692901</v>
       </c>
       <c r="E42">
-        <v>-2.039999999999999</v>
+        <v>-0.9009999999999962</v>
       </c>
       <c r="F42">
-        <v>45.56</v>
+        <v>46.69900000000001</v>
       </c>
       <c r="G42">
         <v>2.94</v>
@@ -4731,28 +4731,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M42">
-        <v>2.473908</v>
+        <v>2.5357557</v>
       </c>
       <c r="N42">
-        <v>13.93833689795918</v>
+        <v>13.87648919795918</v>
       </c>
       <c r="O42">
-        <v>4.111809384897959</v>
+        <v>4.093564313397959</v>
       </c>
       <c r="P42">
-        <v>9.826527513061226</v>
+        <v>9.782924884561226</v>
       </c>
       <c r="Q42">
-        <v>14.02652751306123</v>
+        <v>13.98292488456122</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1193194156262337</v>
+        <v>0.1203154413769638</v>
       </c>
       <c r="T42">
-        <v>1.137321977761806</v>
+        <v>1.152730179351453</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.634137121493274</v>
+        <v>6.472328899017828</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08668152541240862</v>
+        <v>0.08645880144907707</v>
       </c>
       <c r="C43">
-        <v>76.47536706929012</v>
+        <v>75.93598039404402</v>
       </c>
       <c r="D43">
-        <v>120.2343670692901</v>
+        <v>120.833980394044</v>
       </c>
       <c r="E43">
-        <v>-0.9009999999999962</v>
+        <v>0.2380000000000067</v>
       </c>
       <c r="F43">
-        <v>46.69900000000001</v>
+        <v>47.83800000000001</v>
       </c>
       <c r="G43">
         <v>2.94</v>
@@ -4813,28 +4813,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M43">
-        <v>2.5357557</v>
+        <v>2.597603400000001</v>
       </c>
       <c r="N43">
-        <v>13.87648919795918</v>
+        <v>13.81464149795918</v>
       </c>
       <c r="O43">
-        <v>4.093564313397959</v>
+        <v>4.075319241897959</v>
       </c>
       <c r="P43">
-        <v>9.782924884561226</v>
+        <v>9.739322256061225</v>
       </c>
       <c r="Q43">
-        <v>13.98292488456122</v>
+        <v>13.93932225606122</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1203154413769638</v>
+        <v>0.1213458128432363</v>
       </c>
       <c r="T43">
-        <v>1.152730179351453</v>
+        <v>1.168669698237296</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.472328899017828</v>
+        <v>6.318225829993594</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08645880144907708</v>
+        <v>0.08623607748574552</v>
       </c>
       <c r="C44">
-        <v>75.93598039404398</v>
+        <v>75.40260428224992</v>
       </c>
       <c r="D44">
-        <v>120.833980394044</v>
+        <v>121.4396042822499</v>
       </c>
       <c r="E44">
-        <v>0.2379999999999995</v>
+        <v>1.377000000000002</v>
       </c>
       <c r="F44">
-        <v>47.838</v>
+        <v>48.977</v>
       </c>
       <c r="G44">
         <v>2.94</v>
@@ -4895,28 +4895,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M44">
-        <v>2.5976034</v>
+        <v>2.6594511</v>
       </c>
       <c r="N44">
-        <v>13.81464149795918</v>
+        <v>13.75279379795918</v>
       </c>
       <c r="O44">
-        <v>4.075319241897959</v>
+        <v>4.057074170397959</v>
       </c>
       <c r="P44">
-        <v>9.739322256061225</v>
+        <v>9.695719627561225</v>
       </c>
       <c r="Q44">
-        <v>13.93932225606122</v>
+        <v>13.89571962756122</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1213458128432363</v>
+        <v>0.1224123376942904</v>
       </c>
       <c r="T44">
-        <v>1.168669698237296</v>
+        <v>1.185168498487553</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.318225829993595</v>
+        <v>6.171290345575139</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08623607748574552</v>
+        <v>0.08632355352241397</v>
       </c>
       <c r="C45">
-        <v>75.40260428224992</v>
+        <v>74.025019718976</v>
       </c>
       <c r="D45">
-        <v>121.4396042822499</v>
+        <v>121.201019718976</v>
       </c>
       <c r="E45">
-        <v>1.377000000000002</v>
+        <v>2.515999999999998</v>
       </c>
       <c r="F45">
-        <v>48.977</v>
+        <v>50.116</v>
       </c>
       <c r="G45">
         <v>2.94</v>
@@ -4977,45 +4977,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M45">
-        <v>2.6594511</v>
+        <v>2.7714148</v>
       </c>
       <c r="N45">
-        <v>13.75279379795918</v>
+        <v>13.64083009795918</v>
       </c>
       <c r="O45">
-        <v>4.057074170397959</v>
+        <v>4.024044878897959</v>
       </c>
       <c r="P45">
-        <v>9.695719627561225</v>
+        <v>9.616785219061224</v>
       </c>
       <c r="Q45">
-        <v>13.89571962756122</v>
+        <v>13.81678521906122</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1224123376942904</v>
+        <v>0.1235169527185964</v>
       </c>
       <c r="T45">
-        <v>1.185168498487553</v>
+        <v>1.202256541603892</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.295</v>
       </c>
       <c r="W45">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.171290345575139</v>
+        <v>5.921973462059589</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08632355352241397</v>
+        <v>0.0861078795590824</v>
       </c>
       <c r="C46">
-        <v>74.025019718976</v>
+        <v>73.47595675366296</v>
       </c>
       <c r="D46">
-        <v>121.201019718976</v>
+        <v>121.790956753663</v>
       </c>
       <c r="E46">
-        <v>2.515999999999998</v>
+        <v>3.655000000000001</v>
       </c>
       <c r="F46">
-        <v>50.116</v>
+        <v>51.255</v>
       </c>
       <c r="G46">
         <v>2.94</v>
@@ -5059,28 +5059,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M46">
-        <v>2.7714148</v>
+        <v>2.8344015</v>
       </c>
       <c r="N46">
-        <v>13.64083009795918</v>
+        <v>13.57784339795918</v>
       </c>
       <c r="O46">
-        <v>4.024044878897959</v>
+        <v>4.005463802397959</v>
       </c>
       <c r="P46">
-        <v>9.616785219061224</v>
+        <v>9.572379595561225</v>
       </c>
       <c r="Q46">
-        <v>13.81678521906122</v>
+        <v>13.77237959556122</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1235169527185964</v>
+        <v>0.124661735561968</v>
       </c>
       <c r="T46">
-        <v>1.202256541603892</v>
+        <v>1.219965968106279</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.921973462059589</v>
+        <v>5.790374051791598</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0861078795590824</v>
+        <v>0.08589220559575085</v>
       </c>
       <c r="C47">
-        <v>73.47595675366296</v>
+        <v>72.93266482857521</v>
       </c>
       <c r="D47">
-        <v>121.790956753663</v>
+        <v>122.3866648285752</v>
       </c>
       <c r="E47">
-        <v>3.655000000000001</v>
+        <v>4.794000000000004</v>
       </c>
       <c r="F47">
-        <v>51.255</v>
+        <v>52.39400000000001</v>
       </c>
       <c r="G47">
         <v>2.94</v>
@@ -5141,28 +5141,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M47">
-        <v>2.8344015</v>
+        <v>2.8973882</v>
       </c>
       <c r="N47">
-        <v>13.57784339795918</v>
+        <v>13.51485669795918</v>
       </c>
       <c r="O47">
-        <v>4.005463802397959</v>
+        <v>3.986882725897959</v>
       </c>
       <c r="P47">
-        <v>9.572379595561225</v>
+        <v>9.527973972061226</v>
       </c>
       <c r="Q47">
-        <v>13.77237959556122</v>
+        <v>13.72797397206122</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.124661735561968</v>
+        <v>0.125848917769909</v>
       </c>
       <c r="T47">
-        <v>1.219965968106279</v>
+        <v>1.238331299293939</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.790374051791598</v>
+        <v>5.66449635501352</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08589220559575085</v>
+        <v>0.0856765316324193</v>
       </c>
       <c r="C48">
-        <v>72.93266482857521</v>
+        <v>72.39522904247616</v>
       </c>
       <c r="D48">
-        <v>122.3866648285752</v>
+        <v>122.9882290424762</v>
       </c>
       <c r="E48">
-        <v>4.794000000000004</v>
+        <v>5.933000000000007</v>
       </c>
       <c r="F48">
-        <v>52.39400000000001</v>
+        <v>53.53300000000001</v>
       </c>
       <c r="G48">
         <v>2.94</v>
@@ -5223,28 +5223,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M48">
-        <v>2.8973882</v>
+        <v>2.960374900000001</v>
       </c>
       <c r="N48">
-        <v>13.51485669795918</v>
+        <v>13.45186999795918</v>
       </c>
       <c r="O48">
-        <v>3.986882725897959</v>
+        <v>3.968301649397958</v>
       </c>
       <c r="P48">
-        <v>9.527973972061226</v>
+        <v>9.483568348561224</v>
       </c>
       <c r="Q48">
-        <v>13.72797397206122</v>
+        <v>13.68356834856122</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.125848917769909</v>
+        <v>0.1270808993064515</v>
       </c>
       <c r="T48">
-        <v>1.238331299293939</v>
+        <v>1.257389661847172</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.66449635501352</v>
+        <v>5.543975155970678</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0856765316324193</v>
+        <v>0.08546085766908773</v>
       </c>
       <c r="C49">
-        <v>72.39522904247616</v>
+        <v>71.86373617552931</v>
       </c>
       <c r="D49">
-        <v>122.9882290424762</v>
+        <v>123.5957361755293</v>
       </c>
       <c r="E49">
-        <v>5.933000000000007</v>
+        <v>7.072000000000003</v>
       </c>
       <c r="F49">
-        <v>53.53300000000001</v>
+        <v>54.672</v>
       </c>
       <c r="G49">
         <v>2.94</v>
@@ -5305,28 +5305,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M49">
-        <v>2.960374900000001</v>
+        <v>3.0233616</v>
       </c>
       <c r="N49">
-        <v>13.45186999795918</v>
+        <v>13.38888329795918</v>
       </c>
       <c r="O49">
-        <v>3.968301649397958</v>
+        <v>3.949720572897959</v>
       </c>
       <c r="P49">
-        <v>9.483568348561224</v>
+        <v>9.439162725061223</v>
       </c>
       <c r="Q49">
-        <v>13.68356834856122</v>
+        <v>13.63916272506122</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1270808993064515</v>
+        <v>0.1283602647482456</v>
       </c>
       <c r="T49">
-        <v>1.257389661847172</v>
+        <v>1.27718103834476</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.543975155970678</v>
+        <v>5.428475673554622</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08546085766908773</v>
+        <v>0.08524518370575616</v>
       </c>
       <c r="C50">
-        <v>71.86373617552931</v>
+        <v>71.33827473103125</v>
       </c>
       <c r="D50">
-        <v>123.5957361755293</v>
+        <v>124.2092747310312</v>
       </c>
       <c r="E50">
-        <v>7.072000000000003</v>
+        <v>8.210999999999999</v>
       </c>
       <c r="F50">
-        <v>54.672</v>
+        <v>55.811</v>
       </c>
       <c r="G50">
         <v>2.94</v>
@@ -5387,28 +5387,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M50">
-        <v>3.0233616</v>
+        <v>3.0863483</v>
       </c>
       <c r="N50">
-        <v>13.38888329795918</v>
+        <v>13.32589659795918</v>
       </c>
       <c r="O50">
-        <v>3.949720572897959</v>
+        <v>3.931139496397959</v>
       </c>
       <c r="P50">
-        <v>9.439162725061223</v>
+        <v>9.394757101561224</v>
       </c>
       <c r="Q50">
-        <v>13.63916272506122</v>
+        <v>13.59475710156122</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1283602647482456</v>
+        <v>0.1296898013838356</v>
       </c>
       <c r="T50">
-        <v>1.27718103834476</v>
+        <v>1.297748547254018</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.428475673554622</v>
+        <v>5.317690455726978</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08524518370575616</v>
+        <v>0.08502950974242462</v>
       </c>
       <c r="C51">
-        <v>71.33827473103125</v>
+        <v>70.81893497839373</v>
       </c>
       <c r="D51">
-        <v>124.2092747310312</v>
+        <v>124.8289349783937</v>
       </c>
       <c r="E51">
-        <v>8.210999999999999</v>
+        <v>9.350000000000001</v>
       </c>
       <c r="F51">
-        <v>55.811</v>
+        <v>56.95</v>
       </c>
       <c r="G51">
         <v>2.94</v>
@@ -5469,28 +5469,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M51">
-        <v>3.0863483</v>
+        <v>3.149335</v>
       </c>
       <c r="N51">
-        <v>13.32589659795918</v>
+        <v>13.26290989795918</v>
       </c>
       <c r="O51">
-        <v>3.931139496397959</v>
+        <v>3.912558419897959</v>
       </c>
       <c r="P51">
-        <v>9.394757101561224</v>
+        <v>9.350351478061224</v>
       </c>
       <c r="Q51">
-        <v>13.59475710156122</v>
+        <v>13.55035147806122</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1296898013838356</v>
+        <v>0.1310725194848492</v>
       </c>
       <c r="T51">
-        <v>1.297748547254018</v>
+        <v>1.319138756519646</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.317690455726978</v>
+        <v>5.211336646612438</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08502950974242462</v>
+        <v>0.08481383577909306</v>
       </c>
       <c r="C52">
-        <v>70.81893497839373</v>
+        <v>70.30580899741932</v>
       </c>
       <c r="D52">
-        <v>124.8289349783937</v>
+        <v>125.4548089974193</v>
       </c>
       <c r="E52">
-        <v>9.350000000000001</v>
+        <v>10.489</v>
       </c>
       <c r="F52">
-        <v>56.95</v>
+        <v>58.08900000000001</v>
       </c>
       <c r="G52">
         <v>2.94</v>
@@ -5551,28 +5551,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M52">
-        <v>3.149335</v>
+        <v>3.2123217</v>
       </c>
       <c r="N52">
-        <v>13.26290989795918</v>
+        <v>13.19992319795918</v>
       </c>
       <c r="O52">
-        <v>3.912558419897959</v>
+        <v>3.893977343397959</v>
       </c>
       <c r="P52">
-        <v>9.350351478061224</v>
+        <v>9.305945854561225</v>
       </c>
       <c r="Q52">
-        <v>13.55035147806122</v>
+        <v>13.50594585456122</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1310725194848492</v>
+        <v>0.1325116750593736</v>
       </c>
       <c r="T52">
-        <v>1.319138756519646</v>
+        <v>1.341402035551218</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.211336646612438</v>
+        <v>5.109153575110233</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08481383577909306</v>
+        <v>0.08459816181576152</v>
       </c>
       <c r="C53">
-        <v>70.30580899741932</v>
+        <v>69.79899072391461</v>
       </c>
       <c r="D53">
-        <v>125.4548089974193</v>
+        <v>126.0869907239146</v>
       </c>
       <c r="E53">
-        <v>10.489</v>
+        <v>11.628</v>
       </c>
       <c r="F53">
-        <v>58.08900000000001</v>
+        <v>59.228</v>
       </c>
       <c r="G53">
         <v>2.94</v>
@@ -5633,28 +5633,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M53">
-        <v>3.2123217</v>
+        <v>3.2753084</v>
       </c>
       <c r="N53">
-        <v>13.19992319795918</v>
+        <v>13.13693649795918</v>
       </c>
       <c r="O53">
-        <v>3.893977343397959</v>
+        <v>3.875396266897959</v>
       </c>
       <c r="P53">
-        <v>9.305945854561225</v>
+        <v>9.261540231061225</v>
       </c>
       <c r="Q53">
-        <v>13.50594585456122</v>
+        <v>13.46154023106122</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1325116750593736</v>
+        <v>0.1340107954495031</v>
       </c>
       <c r="T53">
-        <v>1.341402035551218</v>
+        <v>1.364592951209106</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.109153575110233</v>
+        <v>5.010900621742729</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08459816181576152</v>
+        <v>0.08438248785242997</v>
       </c>
       <c r="C54">
-        <v>69.79899072391461</v>
+        <v>69.29857599669081</v>
       </c>
       <c r="D54">
-        <v>126.0869907239146</v>
+        <v>126.7255759966908</v>
       </c>
       <c r="E54">
-        <v>11.628</v>
+        <v>12.767</v>
       </c>
       <c r="F54">
-        <v>59.228</v>
+        <v>60.367</v>
       </c>
       <c r="G54">
         <v>2.94</v>
@@ -5715,28 +5715,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M54">
-        <v>3.2753084</v>
+        <v>3.3382951</v>
       </c>
       <c r="N54">
-        <v>13.13693649795918</v>
+        <v>13.07394979795918</v>
       </c>
       <c r="O54">
-        <v>3.875396266897959</v>
+        <v>3.856815190397959</v>
       </c>
       <c r="P54">
-        <v>9.261540231061225</v>
+        <v>9.217134607561224</v>
       </c>
       <c r="Q54">
-        <v>13.46154023106122</v>
+        <v>13.41713460756122</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1340107954495031</v>
+        <v>0.1355737081966595</v>
       </c>
       <c r="T54">
-        <v>1.364592951209106</v>
+        <v>1.388770714341798</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.010900621742729</v>
+        <v>4.916355326992866</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08438248785242997</v>
+        <v>0.08416681388909839</v>
       </c>
       <c r="C55">
-        <v>69.29857599669081</v>
+        <v>68.80466260599889</v>
       </c>
       <c r="D55">
-        <v>126.7255759966908</v>
+        <v>127.3706626059989</v>
       </c>
       <c r="E55">
-        <v>12.767</v>
+        <v>13.90600000000001</v>
       </c>
       <c r="F55">
-        <v>60.367</v>
+        <v>61.50600000000001</v>
       </c>
       <c r="G55">
         <v>2.94</v>
@@ -5797,28 +5797,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M55">
-        <v>3.3382951</v>
+        <v>3.4012818</v>
       </c>
       <c r="N55">
-        <v>13.07394979795918</v>
+        <v>13.01096309795918</v>
       </c>
       <c r="O55">
-        <v>3.856815190397959</v>
+        <v>3.838234113897959</v>
       </c>
       <c r="P55">
-        <v>9.217134607561224</v>
+        <v>9.172728984061225</v>
       </c>
       <c r="Q55">
-        <v>13.41713460756122</v>
+        <v>13.37272898406122</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1355737081966595</v>
+        <v>0.137204573671953</v>
       </c>
       <c r="T55">
-        <v>1.388770714341798</v>
+        <v>1.413999684567215</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.916355326992866</v>
+        <v>4.825311709826332</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08416681388909839</v>
+        <v>0.08395113992576683</v>
       </c>
       <c r="C56">
-        <v>68.80466260599889</v>
+        <v>68.31735034345172</v>
       </c>
       <c r="D56">
-        <v>127.3706626059989</v>
+        <v>128.0223503434517</v>
       </c>
       <c r="E56">
-        <v>13.90600000000001</v>
+        <v>15.04500000000001</v>
       </c>
       <c r="F56">
-        <v>61.50600000000001</v>
+        <v>62.64500000000001</v>
       </c>
       <c r="G56">
         <v>2.94</v>
@@ -5879,28 +5879,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M56">
-        <v>3.4012818</v>
+        <v>3.464268500000001</v>
       </c>
       <c r="N56">
-        <v>13.01096309795918</v>
+        <v>12.94797639795918</v>
       </c>
       <c r="O56">
-        <v>3.838234113897959</v>
+        <v>3.819653037397959</v>
       </c>
       <c r="P56">
-        <v>9.172728984061225</v>
+        <v>9.128323360561224</v>
       </c>
       <c r="Q56">
-        <v>13.37272898406122</v>
+        <v>13.32832336056122</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.137204573671953</v>
+        <v>0.1389079220572596</v>
       </c>
       <c r="T56">
-        <v>1.413999684567215</v>
+        <v>1.440349942358206</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.825311709826332</v>
+        <v>4.73757876964767</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08395113992576683</v>
+        <v>0.08373546596243528</v>
       </c>
       <c r="C57">
-        <v>68.31735034345172</v>
+        <v>67.83674105348764</v>
       </c>
       <c r="D57">
-        <v>128.0223503434517</v>
+        <v>128.6807410534877</v>
       </c>
       <c r="E57">
-        <v>15.04500000000001</v>
+        <v>16.184</v>
       </c>
       <c r="F57">
-        <v>62.64500000000001</v>
+        <v>63.78400000000001</v>
       </c>
       <c r="G57">
         <v>2.94</v>
@@ -5961,28 +5961,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M57">
-        <v>3.464268500000001</v>
+        <v>3.5272552</v>
       </c>
       <c r="N57">
-        <v>12.94797639795918</v>
+        <v>12.88498969795918</v>
       </c>
       <c r="O57">
-        <v>3.819653037397959</v>
+        <v>3.801071960897959</v>
       </c>
       <c r="P57">
-        <v>9.128323360561224</v>
+        <v>9.083917737061224</v>
       </c>
       <c r="Q57">
-        <v>13.32832336056122</v>
+        <v>13.28391773706122</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1389079220572596</v>
+        <v>0.1406886953691711</v>
       </c>
       <c r="T57">
-        <v>1.440349942358206</v>
+        <v>1.467897939139697</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.73757876964767</v>
+        <v>4.652979148761105</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08373546596243528</v>
+        <v>0.08351979199910373</v>
       </c>
       <c r="C58">
-        <v>67.83674105348764</v>
+        <v>67.36293868642871</v>
       </c>
       <c r="D58">
-        <v>128.6807410534877</v>
+        <v>129.3459386864287</v>
       </c>
       <c r="E58">
-        <v>16.184</v>
+        <v>17.32300000000001</v>
       </c>
       <c r="F58">
-        <v>63.78400000000001</v>
+        <v>64.92300000000002</v>
       </c>
       <c r="G58">
         <v>2.94</v>
@@ -6043,28 +6043,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M58">
-        <v>3.5272552</v>
+        <v>3.590241900000001</v>
       </c>
       <c r="N58">
-        <v>12.88498969795918</v>
+        <v>12.82200299795918</v>
       </c>
       <c r="O58">
-        <v>3.801071960897959</v>
+        <v>3.782490884397959</v>
       </c>
       <c r="P58">
-        <v>9.083917737061224</v>
+        <v>9.039512113561225</v>
       </c>
       <c r="Q58">
-        <v>13.28391773706122</v>
+        <v>13.23951211356122</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1406886953691711</v>
+        <v>0.1425522953467528</v>
       </c>
       <c r="T58">
-        <v>1.467897939139697</v>
+        <v>1.496727238097071</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.652979148761105</v>
+        <v>4.571347935624945</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08351979199910373</v>
+        <v>0.08432636803577215</v>
       </c>
       <c r="C59">
-        <v>67.36293868642871</v>
+        <v>63.77080212348378</v>
       </c>
       <c r="D59">
-        <v>129.3459386864287</v>
+        <v>126.8928021234838</v>
       </c>
       <c r="E59">
-        <v>17.32300000000001</v>
+        <v>18.46200000000001</v>
       </c>
       <c r="F59">
-        <v>64.92300000000002</v>
+        <v>66.06200000000001</v>
       </c>
       <c r="G59">
         <v>2.94</v>
@@ -6125,45 +6125,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M59">
-        <v>3.590241900000001</v>
+        <v>3.818383600000001</v>
       </c>
       <c r="N59">
-        <v>12.82200299795918</v>
+        <v>12.59386129795918</v>
       </c>
       <c r="O59">
-        <v>3.782490884397959</v>
+        <v>3.715189082897959</v>
       </c>
       <c r="P59">
-        <v>9.039512113561225</v>
+        <v>8.878672215061224</v>
       </c>
       <c r="Q59">
-        <v>13.23951211356122</v>
+        <v>13.07867221506122</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1425522953467528</v>
+        <v>0.1445046381804099</v>
       </c>
       <c r="T59">
-        <v>1.496727238097071</v>
+        <v>1.52692936081432</v>
       </c>
       <c r="U59">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V59">
         <v>0.295</v>
       </c>
       <c r="W59">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.571347935624945</v>
+        <v>4.298217941738274</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08432636803577215</v>
+        <v>0.0841283190724406</v>
       </c>
       <c r="C60">
-        <v>63.77080212348379</v>
+        <v>63.22549298134183</v>
       </c>
       <c r="D60">
-        <v>126.8928021234838</v>
+        <v>127.4864929813418</v>
       </c>
       <c r="E60">
-        <v>18.462</v>
+        <v>19.60099999999999</v>
       </c>
       <c r="F60">
-        <v>66.062</v>
+        <v>67.20099999999999</v>
       </c>
       <c r="G60">
         <v>2.94</v>
@@ -6207,28 +6207,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M60">
-        <v>3.8183836</v>
+        <v>3.8842178</v>
       </c>
       <c r="N60">
-        <v>12.59386129795918</v>
+        <v>12.52802709795918</v>
       </c>
       <c r="O60">
-        <v>3.715189082897959</v>
+        <v>3.695767993897959</v>
       </c>
       <c r="P60">
-        <v>8.878672215061224</v>
+        <v>8.832259104061224</v>
       </c>
       <c r="Q60">
-        <v>13.07867221506122</v>
+        <v>13.03225910406122</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1445046381804099</v>
+        <v>0.1465522172498551</v>
       </c>
       <c r="T60">
-        <v>1.52692936081432</v>
+        <v>1.558604757810459</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.298217941738274</v>
+        <v>4.225366790183388</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0841283190724406</v>
+        <v>0.08393027010910906</v>
       </c>
       <c r="C61">
-        <v>63.22549298134183</v>
+        <v>62.68576533270641</v>
       </c>
       <c r="D61">
-        <v>127.4864929813418</v>
+        <v>128.0857653327064</v>
       </c>
       <c r="E61">
-        <v>19.60099999999999</v>
+        <v>20.74</v>
       </c>
       <c r="F61">
-        <v>67.20099999999999</v>
+        <v>68.34</v>
       </c>
       <c r="G61">
         <v>2.94</v>
@@ -6289,28 +6289,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M61">
-        <v>3.8842178</v>
+        <v>3.950052</v>
       </c>
       <c r="N61">
-        <v>12.52802709795918</v>
+        <v>12.46219289795918</v>
       </c>
       <c r="O61">
-        <v>3.695767993897959</v>
+        <v>3.676346904897959</v>
       </c>
       <c r="P61">
-        <v>8.832259104061224</v>
+        <v>8.785845993061224</v>
       </c>
       <c r="Q61">
-        <v>13.03225910406122</v>
+        <v>12.98584599306122</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1465522172498551</v>
+        <v>0.1487021752727726</v>
       </c>
       <c r="T61">
-        <v>1.558604757810459</v>
+        <v>1.591863924656405</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.225366790183388</v>
+        <v>4.154944010346998</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08393027010910906</v>
+        <v>0.08373222114577748</v>
       </c>
       <c r="C62">
-        <v>62.68576533270641</v>
+        <v>62.1516982596488</v>
       </c>
       <c r="D62">
-        <v>128.0857653327064</v>
+        <v>128.6906982596488</v>
       </c>
       <c r="E62">
-        <v>20.74</v>
+        <v>21.879</v>
       </c>
       <c r="F62">
-        <v>68.34</v>
+        <v>69.479</v>
       </c>
       <c r="G62">
         <v>2.94</v>
@@ -6371,28 +6371,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M62">
-        <v>3.950052</v>
+        <v>4.015886200000001</v>
       </c>
       <c r="N62">
-        <v>12.46219289795918</v>
+        <v>12.39635869795918</v>
       </c>
       <c r="O62">
-        <v>3.676346904897959</v>
+        <v>3.656925815897959</v>
       </c>
       <c r="P62">
-        <v>8.785845993061224</v>
+        <v>8.739432882061225</v>
       </c>
       <c r="Q62">
-        <v>12.98584599306122</v>
+        <v>12.93943288206122</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1487021752727726</v>
+        <v>0.1509623875532756</v>
       </c>
       <c r="T62">
-        <v>1.591863924656405</v>
+        <v>1.626828689802144</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.154944010346998</v>
+        <v>4.086830174111801</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08373222114577748</v>
+        <v>0.08353417218244594</v>
       </c>
       <c r="C63">
-        <v>62.1516982596488</v>
+        <v>61.62337234530791</v>
       </c>
       <c r="D63">
-        <v>128.6906982596488</v>
+        <v>129.3013723453079</v>
       </c>
       <c r="E63">
-        <v>21.879</v>
+        <v>23.01800000000001</v>
       </c>
       <c r="F63">
-        <v>69.479</v>
+        <v>70.61800000000001</v>
       </c>
       <c r="G63">
         <v>2.94</v>
@@ -6453,28 +6453,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M63">
-        <v>4.015886200000001</v>
+        <v>4.081720400000001</v>
       </c>
       <c r="N63">
-        <v>12.39635869795918</v>
+        <v>12.33052449795918</v>
       </c>
       <c r="O63">
-        <v>3.656925815897959</v>
+        <v>3.637504726897959</v>
       </c>
       <c r="P63">
-        <v>8.739432882061225</v>
+        <v>8.693019771061223</v>
       </c>
       <c r="Q63">
-        <v>12.93943288206122</v>
+        <v>12.89301977106122</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1509623875532756</v>
+        <v>0.1533415583748577</v>
       </c>
       <c r="T63">
-        <v>1.626828689802144</v>
+        <v>1.663633705745027</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.086830174111801</v>
+        <v>4.02091355840032</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08353417218244594</v>
+        <v>0.08489064821911436</v>
       </c>
       <c r="C64">
-        <v>61.62337234530791</v>
+        <v>56.4141852138053</v>
       </c>
       <c r="D64">
-        <v>129.3013723453079</v>
+        <v>125.2311852138053</v>
       </c>
       <c r="E64">
-        <v>23.01800000000001</v>
+        <v>24.157</v>
       </c>
       <c r="F64">
-        <v>70.61800000000001</v>
+        <v>71.75700000000001</v>
       </c>
       <c r="G64">
         <v>2.94</v>
@@ -6535,45 +6535,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M64">
-        <v>4.081720400000001</v>
+        <v>4.398704100000001</v>
       </c>
       <c r="N64">
-        <v>12.33052449795918</v>
+        <v>12.01354079795918</v>
       </c>
       <c r="O64">
-        <v>3.637504726897959</v>
+        <v>3.543994535397959</v>
       </c>
       <c r="P64">
-        <v>8.693019771061223</v>
+        <v>8.469546262561225</v>
       </c>
       <c r="Q64">
-        <v>12.89301977106122</v>
+        <v>12.66954626256122</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1533415583748577</v>
+        <v>0.1558493330246334</v>
       </c>
       <c r="T64">
-        <v>1.663633705745027</v>
+        <v>1.702428182009146</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.295</v>
       </c>
       <c r="W64">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.02091355840032</v>
+        <v>3.731154568446462</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08489064821911436</v>
+        <v>0.08471727425578282</v>
       </c>
       <c r="C65">
-        <v>56.4141852138053</v>
+        <v>55.78106381432947</v>
       </c>
       <c r="D65">
-        <v>125.2311852138053</v>
+        <v>125.7370638143295</v>
       </c>
       <c r="E65">
-        <v>24.157</v>
+        <v>25.296</v>
       </c>
       <c r="F65">
-        <v>71.75700000000001</v>
+        <v>72.896</v>
       </c>
       <c r="G65">
         <v>2.94</v>
@@ -6617,28 +6617,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M65">
-        <v>4.398704100000001</v>
+        <v>4.4685248</v>
       </c>
       <c r="N65">
-        <v>12.01354079795918</v>
+        <v>11.94372009795918</v>
       </c>
       <c r="O65">
-        <v>3.543994535397959</v>
+        <v>3.523397428897959</v>
       </c>
       <c r="P65">
-        <v>8.469546262561225</v>
+        <v>8.420322669061225</v>
       </c>
       <c r="Q65">
-        <v>12.66954626256122</v>
+        <v>12.62032266906122</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1558493330246334</v>
+        <v>0.1584964284882856</v>
       </c>
       <c r="T65">
-        <v>1.702428182009146</v>
+        <v>1.743377906954606</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.731154568446462</v>
+        <v>3.672855278314486</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08471727425578282</v>
+        <v>0.08454390029245126</v>
       </c>
       <c r="C66">
-        <v>55.78106381432947</v>
+        <v>55.15204604330596</v>
       </c>
       <c r="D66">
-        <v>125.7370638143295</v>
+        <v>126.247046043306</v>
       </c>
       <c r="E66">
-        <v>25.296</v>
+        <v>26.43500000000001</v>
       </c>
       <c r="F66">
-        <v>72.896</v>
+        <v>74.03500000000001</v>
       </c>
       <c r="G66">
         <v>2.94</v>
@@ -6699,28 +6699,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M66">
-        <v>4.4685248</v>
+        <v>4.538345500000001</v>
       </c>
       <c r="N66">
-        <v>11.94372009795918</v>
+        <v>11.87389939795918</v>
       </c>
       <c r="O66">
-        <v>3.523397428897959</v>
+        <v>3.502800322397958</v>
       </c>
       <c r="P66">
-        <v>8.420322669061225</v>
+        <v>8.371099075561224</v>
       </c>
       <c r="Q66">
-        <v>12.62032266906122</v>
+        <v>12.57109907556122</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1584964284882856</v>
+        <v>0.1612947865498607</v>
       </c>
       <c r="T66">
-        <v>1.743377906954606</v>
+        <v>1.786667616182663</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.672855278314486</v>
+        <v>3.616349812494262</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08454390029245126</v>
+        <v>0.0843705263291197</v>
       </c>
       <c r="C67">
-        <v>55.15204604330596</v>
+        <v>54.52718203631781</v>
       </c>
       <c r="D67">
-        <v>126.247046043306</v>
+        <v>126.7611820363178</v>
       </c>
       <c r="E67">
-        <v>26.43500000000001</v>
+        <v>27.57400000000001</v>
       </c>
       <c r="F67">
-        <v>74.03500000000001</v>
+        <v>75.17400000000001</v>
       </c>
       <c r="G67">
         <v>2.94</v>
@@ -6781,28 +6781,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M67">
-        <v>4.538345500000001</v>
+        <v>4.6081662</v>
       </c>
       <c r="N67">
-        <v>11.87389939795918</v>
+        <v>11.80407869795918</v>
       </c>
       <c r="O67">
-        <v>3.502800322397958</v>
+        <v>3.482203215897959</v>
       </c>
       <c r="P67">
-        <v>8.371099075561224</v>
+        <v>8.321875482061225</v>
       </c>
       <c r="Q67">
-        <v>12.57109907556122</v>
+        <v>12.52187548206122</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1612947865498607</v>
+        <v>0.1642577539091756</v>
       </c>
       <c r="T67">
-        <v>1.786667616182663</v>
+        <v>1.832503778894723</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.616349812494262</v>
+        <v>3.561556633517077</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0843705263291197</v>
+        <v>0.08419715236578813</v>
       </c>
       <c r="C68">
-        <v>54.52718203631781</v>
+        <v>53.90652274898831</v>
       </c>
       <c r="D68">
-        <v>126.7611820363178</v>
+        <v>127.2795227489883</v>
       </c>
       <c r="E68">
-        <v>27.57400000000001</v>
+        <v>28.713</v>
       </c>
       <c r="F68">
-        <v>75.17400000000001</v>
+        <v>76.313</v>
       </c>
       <c r="G68">
         <v>2.94</v>
@@ -6863,28 +6863,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M68">
-        <v>4.6081662</v>
+        <v>4.677986900000001</v>
       </c>
       <c r="N68">
-        <v>11.80407869795918</v>
+        <v>11.73425799795918</v>
       </c>
       <c r="O68">
-        <v>3.482203215897959</v>
+        <v>3.461606109397959</v>
       </c>
       <c r="P68">
-        <v>8.321875482061225</v>
+        <v>8.272651888561224</v>
       </c>
       <c r="Q68">
-        <v>12.52187548206122</v>
+        <v>12.47265188856122</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1642577539091756</v>
+        <v>0.1674002950478428</v>
       </c>
       <c r="T68">
-        <v>1.832503778894723</v>
+        <v>1.88111789086206</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.561556633517077</v>
+        <v>3.508399071822792</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08419715236578813</v>
+        <v>0.0853660984024566</v>
       </c>
       <c r="C69">
-        <v>53.90652274898831</v>
+        <v>49.35255448788322</v>
       </c>
       <c r="D69">
-        <v>127.2795227489883</v>
+        <v>123.8645544878832</v>
       </c>
       <c r="E69">
-        <v>28.713</v>
+        <v>29.85200000000001</v>
       </c>
       <c r="F69">
-        <v>76.313</v>
+        <v>77.45200000000001</v>
       </c>
       <c r="G69">
         <v>2.94</v>
@@ -6945,45 +6945,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M69">
-        <v>4.677986900000001</v>
+        <v>4.964673200000001</v>
       </c>
       <c r="N69">
-        <v>11.73425799795918</v>
+        <v>11.44757169795918</v>
       </c>
       <c r="O69">
-        <v>3.461606109397959</v>
+        <v>3.377033650897959</v>
       </c>
       <c r="P69">
-        <v>8.272651888561224</v>
+        <v>8.070538047061225</v>
       </c>
       <c r="Q69">
-        <v>12.47265188856122</v>
+        <v>12.27053804706122</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1674002950478428</v>
+        <v>0.1707392450076768</v>
       </c>
       <c r="T69">
-        <v>1.88111789086206</v>
+        <v>1.932770384827355</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.295</v>
       </c>
       <c r="W69">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.508399071822792</v>
+        <v>3.305805686859546</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0853660984024566</v>
+        <v>0.08521246443912503</v>
       </c>
       <c r="C70">
-        <v>49.35255448788322</v>
+        <v>48.65188541585921</v>
       </c>
       <c r="D70">
-        <v>123.8645544878832</v>
+        <v>124.3028854158592</v>
       </c>
       <c r="E70">
-        <v>29.85200000000001</v>
+        <v>30.99100000000001</v>
       </c>
       <c r="F70">
-        <v>77.45200000000001</v>
+        <v>78.59100000000001</v>
       </c>
       <c r="G70">
         <v>2.94</v>
@@ -7027,28 +7027,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M70">
-        <v>4.964673200000001</v>
+        <v>5.037683100000001</v>
       </c>
       <c r="N70">
-        <v>11.44757169795918</v>
+        <v>11.37456179795918</v>
       </c>
       <c r="O70">
-        <v>3.377033650897959</v>
+        <v>3.355495730397959</v>
       </c>
       <c r="P70">
-        <v>8.070538047061225</v>
+        <v>8.019066067561225</v>
       </c>
       <c r="Q70">
-        <v>12.27053804706122</v>
+        <v>12.21906606756122</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1707392450076768</v>
+        <v>0.1742936110939517</v>
       </c>
       <c r="T70">
-        <v>1.932770384827355</v>
+        <v>1.987755297758154</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.305805686859546</v>
+        <v>3.257895459513756</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08521246443912503</v>
+        <v>0.08505883047579346</v>
       </c>
       <c r="C71">
-        <v>48.65188541585921</v>
+        <v>47.95432968550406</v>
       </c>
       <c r="D71">
-        <v>124.3028854158592</v>
+        <v>124.7443296855041</v>
       </c>
       <c r="E71">
-        <v>30.99100000000001</v>
+        <v>32.13000000000002</v>
       </c>
       <c r="F71">
-        <v>78.59100000000001</v>
+        <v>79.73000000000002</v>
       </c>
       <c r="G71">
         <v>2.94</v>
@@ -7109,28 +7109,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M71">
-        <v>5.037683100000001</v>
+        <v>5.110693000000001</v>
       </c>
       <c r="N71">
-        <v>11.37456179795918</v>
+        <v>11.30155189795918</v>
       </c>
       <c r="O71">
-        <v>3.355495730397959</v>
+        <v>3.333957809897959</v>
       </c>
       <c r="P71">
-        <v>8.019066067561225</v>
+        <v>7.967594088061224</v>
       </c>
       <c r="Q71">
-        <v>12.21906606756122</v>
+        <v>12.16759408806122</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1742936110939517</v>
+        <v>0.1780849349193116</v>
       </c>
       <c r="T71">
-        <v>1.987755297758154</v>
+        <v>2.046405871551005</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.257895459513756</v>
+        <v>3.211354095806416</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08505883047579346</v>
+        <v>0.08490519651246192</v>
       </c>
       <c r="C72">
-        <v>47.95432968550406</v>
+        <v>47.25992058482471</v>
       </c>
       <c r="D72">
-        <v>124.7443296855041</v>
+        <v>125.1889205848247</v>
       </c>
       <c r="E72">
-        <v>32.13000000000002</v>
+        <v>33.26900000000001</v>
       </c>
       <c r="F72">
-        <v>79.73000000000002</v>
+        <v>80.86900000000001</v>
       </c>
       <c r="G72">
         <v>2.94</v>
@@ -7191,28 +7191,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M72">
-        <v>5.110693000000001</v>
+        <v>5.183702900000001</v>
       </c>
       <c r="N72">
-        <v>11.30155189795918</v>
+        <v>11.22854199795918</v>
       </c>
       <c r="O72">
-        <v>3.333957809897959</v>
+        <v>3.312419889397959</v>
       </c>
       <c r="P72">
-        <v>7.967594088061224</v>
+        <v>7.916122108561225</v>
       </c>
       <c r="Q72">
-        <v>12.16759408806122</v>
+        <v>12.11612210856122</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1780849349193116</v>
+        <v>0.182137729353317</v>
       </c>
       <c r="T72">
-        <v>2.046405871551005</v>
+        <v>2.109101312501985</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.211354095806416</v>
+        <v>3.166123756428861</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08490519651246192</v>
+        <v>0.08475156254913035</v>
       </c>
       <c r="C73">
-        <v>47.25992058482473</v>
+        <v>46.56869187808174</v>
       </c>
       <c r="D73">
-        <v>125.1889205848247</v>
+        <v>125.6366918780817</v>
       </c>
       <c r="E73">
-        <v>33.269</v>
+        <v>34.40799999999999</v>
       </c>
       <c r="F73">
-        <v>80.869</v>
+        <v>82.008</v>
       </c>
       <c r="G73">
         <v>2.94</v>
@@ -7273,28 +7273,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M73">
-        <v>5.1837029</v>
+        <v>5.2567128</v>
       </c>
       <c r="N73">
-        <v>11.22854199795918</v>
+        <v>11.15553209795918</v>
       </c>
       <c r="O73">
-        <v>3.312419889397959</v>
+        <v>3.290881968897959</v>
       </c>
       <c r="P73">
-        <v>7.916122108561225</v>
+        <v>7.864650129061225</v>
       </c>
       <c r="Q73">
-        <v>12.11612210856122</v>
+        <v>12.06465012906122</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1821377293533169</v>
+        <v>0.186480009104037</v>
       </c>
       <c r="T73">
-        <v>2.109101312501984</v>
+        <v>2.176274999235176</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.166123756428862</v>
+        <v>3.12214981536735</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08475156254913035</v>
+        <v>0.0845979285857988</v>
       </c>
       <c r="C74">
-        <v>46.56869187808174</v>
+        <v>45.88067781433666</v>
       </c>
       <c r="D74">
-        <v>125.6366918780817</v>
+        <v>126.0876778143367</v>
       </c>
       <c r="E74">
-        <v>34.40799999999999</v>
+        <v>35.547</v>
       </c>
       <c r="F74">
-        <v>82.008</v>
+        <v>83.14700000000001</v>
       </c>
       <c r="G74">
         <v>2.94</v>
@@ -7355,28 +7355,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M74">
-        <v>5.2567128</v>
+        <v>5.3297227</v>
       </c>
       <c r="N74">
-        <v>11.15553209795918</v>
+        <v>11.08252219795918</v>
       </c>
       <c r="O74">
-        <v>3.290881968897959</v>
+        <v>3.269344048397959</v>
       </c>
       <c r="P74">
-        <v>7.864650129061225</v>
+        <v>7.813178149561224</v>
       </c>
       <c r="Q74">
-        <v>12.06465012906122</v>
+        <v>12.01317814956122</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.186480009104037</v>
+        <v>0.1911439392066622</v>
       </c>
       <c r="T74">
-        <v>2.176274999235176</v>
+        <v>2.248424514615271</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.12214981536735</v>
+        <v>3.079380639814372</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0845979285857988</v>
+        <v>0.08444429462246725</v>
       </c>
       <c r="C75">
-        <v>45.88067781433666</v>
+        <v>45.19591313618511</v>
       </c>
       <c r="D75">
-        <v>126.0876778143367</v>
+        <v>126.5419131361851</v>
       </c>
       <c r="E75">
-        <v>35.547</v>
+        <v>36.686</v>
       </c>
       <c r="F75">
-        <v>83.14700000000001</v>
+        <v>84.286</v>
       </c>
       <c r="G75">
         <v>2.94</v>
@@ -7437,28 +7437,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M75">
-        <v>5.3297227</v>
+        <v>5.4027326</v>
       </c>
       <c r="N75">
-        <v>11.08252219795918</v>
+        <v>11.00951229795918</v>
       </c>
       <c r="O75">
-        <v>3.269344048397959</v>
+        <v>3.247806127897959</v>
       </c>
       <c r="P75">
-        <v>7.813178149561224</v>
+        <v>7.761706170061224</v>
       </c>
       <c r="Q75">
-        <v>12.01317814956122</v>
+        <v>11.96170617006122</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1911439392066622</v>
+        <v>0.1961666331633355</v>
       </c>
       <c r="T75">
-        <v>2.248424514615271</v>
+        <v>2.326123992716912</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.079380639814372</v>
+        <v>3.037767387924989</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08444429462246725</v>
+        <v>0.0884149106591357</v>
       </c>
       <c r="C76">
-        <v>45.19591313618511</v>
+        <v>33.27859679139155</v>
       </c>
       <c r="D76">
-        <v>126.5419131361851</v>
+        <v>115.7635967913916</v>
       </c>
       <c r="E76">
-        <v>36.686</v>
+        <v>37.82500000000001</v>
       </c>
       <c r="F76">
-        <v>84.286</v>
+        <v>85.42500000000001</v>
       </c>
       <c r="G76">
         <v>2.94</v>
@@ -7519,45 +7519,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M76">
-        <v>5.4027326</v>
+        <v>6.142057500000002</v>
       </c>
       <c r="N76">
-        <v>11.00951229795918</v>
+        <v>10.27018739795918</v>
       </c>
       <c r="O76">
-        <v>3.247806127897959</v>
+        <v>3.029705282397959</v>
       </c>
       <c r="P76">
-        <v>7.761706170061224</v>
+        <v>7.240482115561223</v>
       </c>
       <c r="Q76">
-        <v>11.96170617006122</v>
+        <v>11.44048211556122</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1961666331633355</v>
+        <v>0.2015911426365427</v>
       </c>
       <c r="T76">
-        <v>2.326123992716912</v>
+        <v>2.410039429066685</v>
       </c>
       <c r="U76">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V76">
         <v>0.295</v>
       </c>
       <c r="W76">
-        <v>0.04519050000000001</v>
+        <v>0.05068950000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.037767387924989</v>
+        <v>2.672108637530531</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0884149106591357</v>
+        <v>0.08831626669580414</v>
       </c>
       <c r="C77">
-        <v>33.27859679139155</v>
+        <v>32.38507962743363</v>
       </c>
       <c r="D77">
-        <v>115.7635967913916</v>
+        <v>116.0090796274336</v>
       </c>
       <c r="E77">
-        <v>37.82500000000001</v>
+        <v>38.96400000000001</v>
       </c>
       <c r="F77">
-        <v>85.42500000000001</v>
+        <v>86.56400000000001</v>
       </c>
       <c r="G77">
         <v>2.94</v>
@@ -7601,28 +7601,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M77">
-        <v>6.142057500000002</v>
+        <v>6.223951600000001</v>
       </c>
       <c r="N77">
-        <v>10.27018739795918</v>
+        <v>10.18829329795918</v>
       </c>
       <c r="O77">
-        <v>3.029705282397959</v>
+        <v>3.005546522897959</v>
       </c>
       <c r="P77">
-        <v>7.240482115561223</v>
+        <v>7.182746775061224</v>
       </c>
       <c r="Q77">
-        <v>11.44048211556122</v>
+        <v>11.38274677506122</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2015911426365427</v>
+        <v>0.2074676945658505</v>
       </c>
       <c r="T77">
-        <v>2.410039429066685</v>
+        <v>2.500947818445605</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.672108637530531</v>
+        <v>2.636949313352498</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08831626669580414</v>
+        <v>0.08821762273247258</v>
       </c>
       <c r="C78">
-        <v>32.38507962743363</v>
+        <v>31.49260579461622</v>
       </c>
       <c r="D78">
-        <v>116.0090796274336</v>
+        <v>116.2556057946162</v>
       </c>
       <c r="E78">
-        <v>38.96400000000001</v>
+        <v>40.103</v>
       </c>
       <c r="F78">
-        <v>86.56400000000001</v>
+        <v>87.703</v>
       </c>
       <c r="G78">
         <v>2.94</v>
@@ -7683,28 +7683,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M78">
-        <v>6.223951600000001</v>
+        <v>6.305845700000001</v>
       </c>
       <c r="N78">
-        <v>10.18829329795918</v>
+        <v>10.10639919795918</v>
       </c>
       <c r="O78">
-        <v>3.005546522897959</v>
+        <v>2.981387763397959</v>
       </c>
       <c r="P78">
-        <v>7.182746775061224</v>
+        <v>7.125011434561224</v>
       </c>
       <c r="Q78">
-        <v>11.38274677506122</v>
+        <v>11.32501143456122</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2074676945658505</v>
+        <v>0.2138552510107503</v>
       </c>
       <c r="T78">
-        <v>2.500947818445605</v>
+        <v>2.599761285161822</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.636949313352498</v>
+        <v>2.602703218373894</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08821762273247258</v>
+        <v>0.08811897876914102</v>
       </c>
       <c r="C79">
-        <v>31.49260579461622</v>
+        <v>30.60118195852554</v>
       </c>
       <c r="D79">
-        <v>116.2556057946162</v>
+        <v>116.5031819585256</v>
       </c>
       <c r="E79">
-        <v>40.103</v>
+        <v>41.24200000000001</v>
       </c>
       <c r="F79">
-        <v>87.703</v>
+        <v>88.84200000000001</v>
       </c>
       <c r="G79">
         <v>2.94</v>
@@ -7765,28 +7765,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M79">
-        <v>6.305845700000001</v>
+        <v>6.387739800000001</v>
       </c>
       <c r="N79">
-        <v>10.10639919795918</v>
+        <v>10.02450509795918</v>
       </c>
       <c r="O79">
-        <v>2.981387763397959</v>
+        <v>2.957229003897958</v>
       </c>
       <c r="P79">
-        <v>7.125011434561224</v>
+        <v>7.067276094061223</v>
       </c>
       <c r="Q79">
-        <v>11.32501143456122</v>
+        <v>11.26727609406122</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2138552510107503</v>
+        <v>0.2208234944051864</v>
       </c>
       <c r="T79">
-        <v>2.599761285161822</v>
+        <v>2.707557794306786</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.602703218373894</v>
+        <v>2.569335228394741</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08811897876914102</v>
+        <v>0.08802033480580947</v>
       </c>
       <c r="C80">
-        <v>30.60118195852554</v>
+        <v>29.7108148416487</v>
       </c>
       <c r="D80">
-        <v>116.5031819585256</v>
+        <v>116.7518148416487</v>
       </c>
       <c r="E80">
-        <v>41.24200000000001</v>
+        <v>42.38100000000001</v>
       </c>
       <c r="F80">
-        <v>88.84200000000001</v>
+        <v>89.98100000000001</v>
       </c>
       <c r="G80">
         <v>2.94</v>
@@ -7847,28 +7847,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M80">
-        <v>6.387739800000001</v>
+        <v>6.469633900000001</v>
       </c>
       <c r="N80">
-        <v>10.02450509795918</v>
+        <v>9.942610997959182</v>
       </c>
       <c r="O80">
-        <v>2.957229003897958</v>
+        <v>2.933070244397959</v>
       </c>
       <c r="P80">
-        <v>7.067276094061223</v>
+        <v>7.009540753561224</v>
       </c>
       <c r="Q80">
-        <v>11.26727609406122</v>
+        <v>11.20954075356122</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2208234944051864</v>
+        <v>0.2284553800276641</v>
       </c>
       <c r="T80">
-        <v>2.707557794306786</v>
+        <v>2.825620637656033</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.569335228394741</v>
+        <v>2.536811997655568</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08802033480580947</v>
+        <v>0.0879216908424779</v>
       </c>
       <c r="C81">
-        <v>29.7108148416487</v>
+        <v>28.82151122398223</v>
       </c>
       <c r="D81">
-        <v>116.7518148416487</v>
+        <v>117.0015112239822</v>
       </c>
       <c r="E81">
-        <v>42.38100000000001</v>
+        <v>43.52</v>
       </c>
       <c r="F81">
-        <v>89.98100000000001</v>
+        <v>91.12</v>
       </c>
       <c r="G81">
         <v>2.94</v>
@@ -7929,28 +7929,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M81">
-        <v>6.469633900000001</v>
+        <v>6.551528000000001</v>
       </c>
       <c r="N81">
-        <v>9.942610997959182</v>
+        <v>9.860716897959183</v>
       </c>
       <c r="O81">
-        <v>2.933070244397959</v>
+        <v>2.908911484897959</v>
       </c>
       <c r="P81">
-        <v>7.009540753561224</v>
+        <v>6.951805413061224</v>
       </c>
       <c r="Q81">
-        <v>11.20954075356122</v>
+        <v>11.15180541306122</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2284553800276641</v>
+        <v>0.2368504542123895</v>
       </c>
       <c r="T81">
-        <v>2.825620637656033</v>
+        <v>2.955489765340204</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.536811997655568</v>
+        <v>2.505101847684873</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0879216908424779</v>
+        <v>0.09005014187914634</v>
       </c>
       <c r="C82">
-        <v>28.82151122398223</v>
+        <v>22.52143119026913</v>
       </c>
       <c r="D82">
-        <v>117.0015112239822</v>
+        <v>111.8404311902691</v>
       </c>
       <c r="E82">
-        <v>43.52</v>
+        <v>44.65900000000001</v>
       </c>
       <c r="F82">
-        <v>91.12</v>
+        <v>92.25900000000001</v>
       </c>
       <c r="G82">
         <v>2.94</v>
@@ -8011,45 +8011,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M82">
-        <v>6.551528000000001</v>
+        <v>6.993232200000001</v>
       </c>
       <c r="N82">
-        <v>9.860716897959183</v>
+        <v>9.419012697959182</v>
       </c>
       <c r="O82">
-        <v>2.908911484897959</v>
+        <v>2.778608745897959</v>
       </c>
       <c r="P82">
-        <v>6.951805413061224</v>
+        <v>6.640403952061224</v>
       </c>
       <c r="Q82">
-        <v>11.15180541306122</v>
+        <v>10.84040395206122</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2368504542123895</v>
+        <v>0.2461292204165597</v>
       </c>
       <c r="T82">
-        <v>2.955489765340204</v>
+        <v>3.099029327517446</v>
       </c>
       <c r="U82">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.295</v>
       </c>
       <c r="W82">
-        <v>0.05068950000000001</v>
+        <v>0.05343900000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.505101847684873</v>
+        <v>2.346875440223361</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09005014187914634</v>
+        <v>0.08997899291581478</v>
       </c>
       <c r="C83">
-        <v>22.52143119026913</v>
+        <v>21.54758694896583</v>
       </c>
       <c r="D83">
-        <v>111.8404311902691</v>
+        <v>112.0055869489658</v>
       </c>
       <c r="E83">
-        <v>44.65900000000001</v>
+        <v>45.79800000000001</v>
       </c>
       <c r="F83">
-        <v>92.25900000000001</v>
+        <v>93.39800000000001</v>
       </c>
       <c r="G83">
         <v>2.94</v>
@@ -8093,28 +8093,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M83">
-        <v>6.993232200000001</v>
+        <v>7.079568400000001</v>
       </c>
       <c r="N83">
-        <v>9.419012697959182</v>
+        <v>9.332676497959183</v>
       </c>
       <c r="O83">
-        <v>2.778608745897959</v>
+        <v>2.753139566897959</v>
       </c>
       <c r="P83">
-        <v>6.640403952061224</v>
+        <v>6.579536931061224</v>
       </c>
       <c r="Q83">
-        <v>10.84040395206122</v>
+        <v>10.77953693106122</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2461292204165597</v>
+        <v>0.2564389606434155</v>
       </c>
       <c r="T83">
-        <v>3.099029327517446</v>
+        <v>3.258517729936604</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.346875440223361</v>
+        <v>2.318255008025515</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08997899291581478</v>
+        <v>0.08990784395248323</v>
       </c>
       <c r="C84">
-        <v>21.54758694896583</v>
+        <v>20.57423120298121</v>
       </c>
       <c r="D84">
-        <v>112.0055869489658</v>
+        <v>112.1712312029812</v>
       </c>
       <c r="E84">
-        <v>45.79800000000001</v>
+        <v>46.937</v>
       </c>
       <c r="F84">
-        <v>93.39800000000001</v>
+        <v>94.53700000000001</v>
       </c>
       <c r="G84">
         <v>2.94</v>
@@ -8175,28 +8175,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M84">
-        <v>7.079568400000001</v>
+        <v>7.165904600000001</v>
       </c>
       <c r="N84">
-        <v>9.332676497959183</v>
+        <v>9.246340297959183</v>
       </c>
       <c r="O84">
-        <v>2.753139566897959</v>
+        <v>2.727670387897959</v>
       </c>
       <c r="P84">
-        <v>6.579536931061224</v>
+        <v>6.518669910061224</v>
       </c>
       <c r="Q84">
-        <v>10.77953693106122</v>
+        <v>10.71866991006122</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2564389606434155</v>
+        <v>0.2679616114851955</v>
       </c>
       <c r="T84">
-        <v>3.258517729936604</v>
+        <v>3.43676947381684</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.318255008025515</v>
+        <v>2.290324224796292</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08990784395248323</v>
+        <v>0.08983669498915169</v>
       </c>
       <c r="C85">
-        <v>20.57423120298121</v>
+        <v>19.60136612282182</v>
       </c>
       <c r="D85">
-        <v>112.1712312029812</v>
+        <v>112.3373661228218</v>
       </c>
       <c r="E85">
-        <v>46.937</v>
+        <v>48.07600000000001</v>
       </c>
       <c r="F85">
-        <v>94.53700000000001</v>
+        <v>95.67600000000002</v>
       </c>
       <c r="G85">
         <v>2.94</v>
@@ -8257,28 +8257,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M85">
-        <v>7.165904600000001</v>
+        <v>7.252240800000002</v>
       </c>
       <c r="N85">
-        <v>9.246340297959183</v>
+        <v>9.160004097959181</v>
       </c>
       <c r="O85">
-        <v>2.727670387897959</v>
+        <v>2.702201208897958</v>
       </c>
       <c r="P85">
-        <v>6.518669910061224</v>
+        <v>6.457802889061223</v>
       </c>
       <c r="Q85">
-        <v>10.71866991006122</v>
+        <v>10.65780288906122</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2679616114851955</v>
+        <v>0.2809245936821981</v>
       </c>
       <c r="T85">
-        <v>3.43676947381684</v>
+        <v>3.637302685682105</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.290324224796292</v>
+        <v>2.263058460215383</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08983669498915167</v>
+        <v>0.08976554602582011</v>
       </c>
       <c r="C86">
-        <v>19.60136612282184</v>
+        <v>18.62899389187216</v>
       </c>
       <c r="D86">
-        <v>112.3373661228218</v>
+        <v>112.5039938918722</v>
       </c>
       <c r="E86">
-        <v>48.076</v>
+        <v>49.215</v>
       </c>
       <c r="F86">
-        <v>95.676</v>
+        <v>96.815</v>
       </c>
       <c r="G86">
         <v>2.94</v>
@@ -8339,28 +8339,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M86">
-        <v>7.252240800000001</v>
+        <v>7.338577000000001</v>
       </c>
       <c r="N86">
-        <v>9.160004097959183</v>
+        <v>9.073667897959183</v>
       </c>
       <c r="O86">
-        <v>2.702201208897959</v>
+        <v>2.676732029897959</v>
       </c>
       <c r="P86">
-        <v>6.457802889061224</v>
+        <v>6.396935868061224</v>
       </c>
       <c r="Q86">
-        <v>10.65780288906122</v>
+        <v>10.59693586806122</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2809245936821979</v>
+        <v>0.2956159735054674</v>
       </c>
       <c r="T86">
-        <v>3.637302685682103</v>
+        <v>3.864573659129403</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.263058460215384</v>
+        <v>2.236434243036379</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08976554602582011</v>
+        <v>0.08969439706248855</v>
       </c>
       <c r="C87">
-        <v>18.62899389187216</v>
+        <v>17.65711670649004</v>
       </c>
       <c r="D87">
-        <v>112.5039938918722</v>
+        <v>112.6711167064901</v>
       </c>
       <c r="E87">
-        <v>49.215</v>
+        <v>50.35400000000001</v>
       </c>
       <c r="F87">
-        <v>96.815</v>
+        <v>97.95400000000001</v>
       </c>
       <c r="G87">
         <v>2.94</v>
@@ -8421,28 +8421,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M87">
-        <v>7.338577000000001</v>
+        <v>7.424913200000002</v>
       </c>
       <c r="N87">
-        <v>9.073667897959183</v>
+        <v>8.987331697959181</v>
       </c>
       <c r="O87">
-        <v>2.676732029897959</v>
+        <v>2.651262850897958</v>
       </c>
       <c r="P87">
-        <v>6.396935868061224</v>
+        <v>6.336068847061223</v>
       </c>
       <c r="Q87">
-        <v>10.59693586806122</v>
+        <v>10.53606884706122</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2956159735054674</v>
+        <v>0.3124061218749182</v>
       </c>
       <c r="T87">
-        <v>3.864573659129403</v>
+        <v>4.124311914497745</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.236434243036379</v>
+        <v>2.210429193698746</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08969439706248855</v>
+        <v>0.089623248099157</v>
       </c>
       <c r="C88">
-        <v>17.65711670649004</v>
+        <v>16.68573677610351</v>
       </c>
       <c r="D88">
-        <v>112.6711167064901</v>
+        <v>112.8387367761035</v>
       </c>
       <c r="E88">
-        <v>50.35400000000001</v>
+        <v>51.493</v>
       </c>
       <c r="F88">
-        <v>97.95400000000001</v>
+        <v>99.093</v>
       </c>
       <c r="G88">
         <v>2.94</v>
@@ -8503,28 +8503,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M88">
-        <v>7.424913200000002</v>
+        <v>7.511249400000001</v>
       </c>
       <c r="N88">
-        <v>8.987331697959181</v>
+        <v>8.900995497959183</v>
       </c>
       <c r="O88">
-        <v>2.651262850897958</v>
+        <v>2.625793671897959</v>
       </c>
       <c r="P88">
-        <v>6.336068847061223</v>
+        <v>6.275201826061224</v>
       </c>
       <c r="Q88">
-        <v>10.53606884706122</v>
+        <v>10.47520182606122</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3124061218749182</v>
+        <v>0.3317793699935154</v>
       </c>
       <c r="T88">
-        <v>4.124311914497745</v>
+        <v>4.424009901461218</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.210429193698746</v>
+        <v>2.185021961587267</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.089623248099157</v>
+        <v>0.08955209913582543</v>
       </c>
       <c r="C89">
-        <v>16.68573677610351</v>
+        <v>15.714856323308</v>
       </c>
       <c r="D89">
-        <v>112.8387367761035</v>
+        <v>113.006856323308</v>
       </c>
       <c r="E89">
-        <v>51.493</v>
+        <v>52.632</v>
       </c>
       <c r="F89">
-        <v>99.093</v>
+        <v>100.232</v>
       </c>
       <c r="G89">
         <v>2.94</v>
@@ -8585,28 +8585,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M89">
-        <v>7.511249400000001</v>
+        <v>7.5975856</v>
       </c>
       <c r="N89">
-        <v>8.900995497959183</v>
+        <v>8.814659297959183</v>
       </c>
       <c r="O89">
-        <v>2.625793671897959</v>
+        <v>2.600324492897959</v>
       </c>
       <c r="P89">
-        <v>6.275201826061224</v>
+        <v>6.214334805061224</v>
       </c>
       <c r="Q89">
-        <v>10.47520182606122</v>
+        <v>10.41433480506122</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3317793699935154</v>
+        <v>0.3543814927985453</v>
       </c>
       <c r="T89">
-        <v>4.424009901461218</v>
+        <v>4.773657552918602</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.185021961587267</v>
+        <v>2.16019216656923</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08955209913582543</v>
+        <v>0.08948095017249388</v>
       </c>
       <c r="C90">
-        <v>15.714856323308</v>
+        <v>14.74447758396435</v>
       </c>
       <c r="D90">
-        <v>113.006856323308</v>
+        <v>113.1754775839644</v>
       </c>
       <c r="E90">
-        <v>52.632</v>
+        <v>53.77100000000001</v>
       </c>
       <c r="F90">
-        <v>100.232</v>
+        <v>101.371</v>
       </c>
       <c r="G90">
         <v>2.94</v>
@@ -8667,28 +8667,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M90">
-        <v>7.5975856</v>
+        <v>7.683921800000001</v>
       </c>
       <c r="N90">
-        <v>8.814659297959183</v>
+        <v>8.728323097959183</v>
       </c>
       <c r="O90">
-        <v>2.600324492897959</v>
+        <v>2.574855313897959</v>
       </c>
       <c r="P90">
-        <v>6.214334805061224</v>
+        <v>6.153467784061224</v>
       </c>
       <c r="Q90">
-        <v>10.41433480506122</v>
+        <v>10.35346778406122</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3543814927985453</v>
+        <v>0.3810930924772171</v>
       </c>
       <c r="T90">
-        <v>4.773657552918602</v>
+        <v>5.186877504640965</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.16019216656923</v>
+        <v>2.135920344472947</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08948095017249388</v>
+        <v>0.08940980120916234</v>
       </c>
       <c r="C91">
-        <v>14.74447758396435</v>
+        <v>13.77460280729844</v>
       </c>
       <c r="D91">
-        <v>113.1754775839644</v>
+        <v>113.3446028072984</v>
       </c>
       <c r="E91">
-        <v>53.77100000000001</v>
+        <v>54.91</v>
       </c>
       <c r="F91">
-        <v>101.371</v>
+        <v>102.51</v>
       </c>
       <c r="G91">
         <v>2.94</v>
@@ -8749,28 +8749,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M91">
-        <v>7.683921800000001</v>
+        <v>7.770258000000001</v>
       </c>
       <c r="N91">
-        <v>8.728323097959183</v>
+        <v>8.641986897959182</v>
       </c>
       <c r="O91">
-        <v>2.574855313897959</v>
+        <v>2.549386134897958</v>
       </c>
       <c r="P91">
-        <v>6.153467784061224</v>
+        <v>6.092600763061224</v>
       </c>
       <c r="Q91">
-        <v>10.35346778406122</v>
+        <v>10.29260076306122</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3810930924772171</v>
+        <v>0.4131470120916233</v>
       </c>
       <c r="T91">
-        <v>5.186877504640965</v>
+        <v>5.682741446707801</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.135920344472947</v>
+        <v>2.112187896201025</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08940980120916234</v>
+        <v>0.08933865224583078</v>
       </c>
       <c r="C92">
-        <v>13.77460280729844</v>
+        <v>12.80523425600079</v>
       </c>
       <c r="D92">
-        <v>113.3446028072984</v>
+        <v>113.5142342560008</v>
       </c>
       <c r="E92">
-        <v>54.91</v>
+        <v>56.04900000000001</v>
       </c>
       <c r="F92">
-        <v>102.51</v>
+        <v>103.649</v>
       </c>
       <c r="G92">
         <v>2.94</v>
@@ -8831,28 +8831,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M92">
-        <v>7.770258000000001</v>
+        <v>7.856594200000002</v>
       </c>
       <c r="N92">
-        <v>8.641986897959182</v>
+        <v>8.555650697959182</v>
       </c>
       <c r="O92">
-        <v>2.549386134897958</v>
+        <v>2.523916955897958</v>
       </c>
       <c r="P92">
-        <v>6.092600763061224</v>
+        <v>6.031733742061224</v>
       </c>
       <c r="Q92">
-        <v>10.29260076306122</v>
+        <v>10.23173374206122</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4131470120916233</v>
+        <v>0.4523240249536754</v>
       </c>
       <c r="T92">
-        <v>5.682741446707801</v>
+        <v>6.288797375900602</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.112187896201025</v>
+        <v>2.088977040198816</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08933865224583078</v>
+        <v>0.08926750328249922</v>
       </c>
       <c r="C93">
-        <v>12.80523425600079</v>
+        <v>11.83637420632753</v>
       </c>
       <c r="D93">
-        <v>113.5142342560008</v>
+        <v>113.6843742063275</v>
       </c>
       <c r="E93">
-        <v>56.04900000000001</v>
+        <v>57.18800000000001</v>
       </c>
       <c r="F93">
-        <v>103.649</v>
+        <v>104.788</v>
       </c>
       <c r="G93">
         <v>2.94</v>
@@ -8913,28 +8913,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M93">
-        <v>7.856594200000002</v>
+        <v>7.942930400000002</v>
       </c>
       <c r="N93">
-        <v>8.555650697959182</v>
+        <v>8.469314497959182</v>
       </c>
       <c r="O93">
-        <v>2.523916955897958</v>
+        <v>2.498447776897958</v>
       </c>
       <c r="P93">
-        <v>6.031733742061224</v>
+        <v>5.970866721061224</v>
       </c>
       <c r="Q93">
-        <v>10.23173374206122</v>
+        <v>10.17086672106122</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4523240249536754</v>
+        <v>0.5012952910312403</v>
       </c>
       <c r="T93">
-        <v>6.288797375900602</v>
+        <v>7.046367287391602</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.088977040198816</v>
+        <v>2.066270768022742</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08926750328249922</v>
+        <v>0.08919635431916766</v>
       </c>
       <c r="C94">
-        <v>11.83637420632753</v>
+        <v>10.86802494820235</v>
       </c>
       <c r="D94">
-        <v>113.6843742063275</v>
+        <v>113.8550249482024</v>
       </c>
       <c r="E94">
-        <v>57.18800000000001</v>
+        <v>58.32700000000001</v>
       </c>
       <c r="F94">
-        <v>104.788</v>
+        <v>105.927</v>
       </c>
       <c r="G94">
         <v>2.94</v>
@@ -8995,28 +8995,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M94">
-        <v>7.942930400000002</v>
+        <v>8.029266600000001</v>
       </c>
       <c r="N94">
-        <v>8.469314497959182</v>
+        <v>8.382978297959182</v>
       </c>
       <c r="O94">
-        <v>2.498447776897958</v>
+        <v>2.472978597897959</v>
       </c>
       <c r="P94">
-        <v>5.970866721061224</v>
+        <v>5.909999700061224</v>
       </c>
       <c r="Q94">
-        <v>10.17086672106122</v>
+        <v>10.10999970006122</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5012952910312403</v>
+        <v>0.564258347416681</v>
       </c>
       <c r="T94">
-        <v>7.046367287391602</v>
+        <v>8.020385745022889</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.066270768022742</v>
+        <v>2.044052802775185</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08919635431916766</v>
+        <v>0.0891252053558361</v>
       </c>
       <c r="C95">
-        <v>10.86802494820235</v>
+        <v>9.900188785319088</v>
       </c>
       <c r="D95">
-        <v>113.8550249482024</v>
+        <v>114.0261887853191</v>
       </c>
       <c r="E95">
-        <v>58.32700000000001</v>
+        <v>59.46600000000002</v>
       </c>
       <c r="F95">
-        <v>105.927</v>
+        <v>107.066</v>
       </c>
       <c r="G95">
         <v>2.94</v>
@@ -9077,28 +9077,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M95">
-        <v>8.029266600000001</v>
+        <v>8.115602800000001</v>
       </c>
       <c r="N95">
-        <v>8.382978297959182</v>
+        <v>8.296642097959182</v>
       </c>
       <c r="O95">
-        <v>2.472978597897959</v>
+        <v>2.447509418897959</v>
       </c>
       <c r="P95">
-        <v>5.909999700061224</v>
+        <v>5.849132679061224</v>
       </c>
       <c r="Q95">
-        <v>10.10999970006122</v>
+        <v>10.04913267906122</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.564258347416681</v>
+        <v>0.6482090892639354</v>
       </c>
       <c r="T95">
-        <v>8.020385745022889</v>
+        <v>9.319077021864604</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.044052802775185</v>
+        <v>2.02230756019247</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0891252053558361</v>
+        <v>0.08905405639250455</v>
       </c>
       <c r="C96">
-        <v>9.900188785319088</v>
+        <v>8.932868035245519</v>
       </c>
       <c r="D96">
-        <v>114.0261887853191</v>
+        <v>114.1978680352455</v>
       </c>
       <c r="E96">
-        <v>59.46600000000002</v>
+        <v>60.60500000000001</v>
       </c>
       <c r="F96">
-        <v>107.066</v>
+        <v>108.205</v>
       </c>
       <c r="G96">
         <v>2.94</v>
@@ -9159,28 +9159,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M96">
-        <v>8.115602800000001</v>
+        <v>8.201939000000001</v>
       </c>
       <c r="N96">
-        <v>8.296642097959182</v>
+        <v>8.210305897959183</v>
       </c>
       <c r="O96">
-        <v>2.447509418897959</v>
+        <v>2.422040239897959</v>
       </c>
       <c r="P96">
-        <v>5.849132679061224</v>
+        <v>5.788265658061224</v>
       </c>
       <c r="Q96">
-        <v>10.04913267906122</v>
+        <v>9.988265658061223</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6482090892639354</v>
+        <v>0.7657401278500917</v>
       </c>
       <c r="T96">
-        <v>9.319077021864604</v>
+        <v>11.13724480944301</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.02230756019247</v>
+        <v>2.001020112190444</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08905405639250455</v>
+        <v>0.09859346742917298</v>
       </c>
       <c r="C97">
-        <v>8.932868035245519</v>
+        <v>-11.38697210295545</v>
       </c>
       <c r="D97">
-        <v>114.1978680352455</v>
+        <v>95.01702789704456</v>
       </c>
       <c r="E97">
-        <v>60.60500000000001</v>
+        <v>61.74400000000001</v>
       </c>
       <c r="F97">
-        <v>108.205</v>
+        <v>109.344</v>
       </c>
       <c r="G97">
         <v>2.94</v>
@@ -9241,45 +9241,45 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M97">
-        <v>8.201939000000001</v>
+        <v>9.840960000000001</v>
       </c>
       <c r="N97">
-        <v>8.210305897959183</v>
+        <v>6.571284897959183</v>
       </c>
       <c r="O97">
-        <v>2.422040239897959</v>
+        <v>1.938529044897959</v>
       </c>
       <c r="P97">
-        <v>5.788265658061224</v>
+        <v>4.632755853061224</v>
       </c>
       <c r="Q97">
-        <v>9.988265658061223</v>
+        <v>8.832755853061222</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7657401278500917</v>
+        <v>0.942036685729326</v>
       </c>
       <c r="T97">
-        <v>11.13724480944301</v>
+        <v>13.86449649081061</v>
       </c>
       <c r="U97">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V97">
         <v>0.295</v>
       </c>
       <c r="W97">
-        <v>0.05343900000000001</v>
+        <v>0.06345000000000001</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.001020112190444</v>
+        <v>1.667748359708726</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09859346742917299</v>
+        <v>0.09862242846584143</v>
       </c>
       <c r="C98">
-        <v>-11.38697210295548</v>
+        <v>-12.5743985061452</v>
       </c>
       <c r="D98">
-        <v>95.01702789704453</v>
+        <v>94.96860149385481</v>
       </c>
       <c r="E98">
-        <v>61.74400000000001</v>
+        <v>62.883</v>
       </c>
       <c r="F98">
-        <v>109.344</v>
+        <v>110.483</v>
       </c>
       <c r="G98">
         <v>2.94</v>
@@ -9323,28 +9323,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M98">
-        <v>9.840960000000001</v>
+        <v>9.94347</v>
       </c>
       <c r="N98">
-        <v>6.571284897959183</v>
+        <v>6.468774897959184</v>
       </c>
       <c r="O98">
-        <v>1.938529044897959</v>
+        <v>1.908288594897959</v>
       </c>
       <c r="P98">
-        <v>4.632755853061224</v>
+        <v>4.560486303061225</v>
       </c>
       <c r="Q98">
-        <v>8.832755853061222</v>
+        <v>8.760486303061224</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9420366857293238</v>
+        <v>1.235864282194713</v>
       </c>
       <c r="T98">
-        <v>13.86449649081058</v>
+        <v>18.40991595975657</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.667748359708726</v>
+        <v>1.650555077649873</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09862242846584143</v>
+        <v>0.09865138950250987</v>
       </c>
       <c r="C99">
-        <v>-12.5743985061452</v>
+        <v>-13.76177557245343</v>
       </c>
       <c r="D99">
-        <v>94.96860149385481</v>
+        <v>94.92022442754657</v>
       </c>
       <c r="E99">
-        <v>62.883</v>
+        <v>64.02199999999999</v>
       </c>
       <c r="F99">
-        <v>110.483</v>
+        <v>111.622</v>
       </c>
       <c r="G99">
         <v>2.94</v>
@@ -9405,28 +9405,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M99">
-        <v>9.94347</v>
+        <v>10.04598</v>
       </c>
       <c r="N99">
-        <v>6.468774897959184</v>
+        <v>6.366264897959184</v>
       </c>
       <c r="O99">
-        <v>1.908288594897959</v>
+        <v>1.878048144897959</v>
       </c>
       <c r="P99">
-        <v>4.560486303061225</v>
+        <v>4.488216753061224</v>
       </c>
       <c r="Q99">
-        <v>8.760486303061224</v>
+        <v>8.688216753061223</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.235864282194713</v>
+        <v>1.823519475125492</v>
       </c>
       <c r="T99">
-        <v>18.40991595975657</v>
+        <v>27.50075489764855</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.650555077649873</v>
+        <v>1.633712678898344</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09865138950250987</v>
+        <v>0.09868035053917831</v>
       </c>
       <c r="C100">
-        <v>-13.76177557245343</v>
+        <v>-14.94910337723853</v>
       </c>
       <c r="D100">
-        <v>94.92022442754657</v>
+        <v>94.87189662276148</v>
       </c>
       <c r="E100">
-        <v>64.02199999999999</v>
+        <v>65.161</v>
       </c>
       <c r="F100">
-        <v>111.622</v>
+        <v>112.761</v>
       </c>
       <c r="G100">
         <v>2.94</v>
@@ -9487,28 +9487,28 @@
         <v>16.41224489795918</v>
       </c>
       <c r="M100">
-        <v>10.04598</v>
+        <v>10.14849</v>
       </c>
       <c r="N100">
-        <v>6.366264897959184</v>
+        <v>6.263754897959183</v>
       </c>
       <c r="O100">
-        <v>1.878048144897959</v>
+        <v>1.847807694897959</v>
       </c>
       <c r="P100">
-        <v>4.488216753061224</v>
+        <v>4.415947203061224</v>
       </c>
       <c r="Q100">
-        <v>8.688216753061223</v>
+        <v>8.615947203061223</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.823519475125492</v>
+        <v>3.586485053917828</v>
       </c>
       <c r="T100">
-        <v>27.50075489764855</v>
+        <v>54.77327171132449</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.633712678898344</v>
+        <v>1.617210530626643</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09868035053917831</v>
-      </c>
-      <c r="C101">
-        <v>-14.94910337723853</v>
-      </c>
-      <c r="D101">
-        <v>94.87189662276148</v>
-      </c>
-      <c r="E101">
-        <v>65.161</v>
-      </c>
-      <c r="F101">
-        <v>112.761</v>
-      </c>
-      <c r="G101">
-        <v>2.94</v>
-      </c>
-      <c r="H101">
-        <v>66.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>20.61224489795918</v>
-      </c>
-      <c r="K101">
-        <v>4.199999999999999</v>
-      </c>
-      <c r="L101">
-        <v>16.41224489795918</v>
-      </c>
-      <c r="M101">
-        <v>10.14849</v>
-      </c>
-      <c r="N101">
-        <v>6.263754897959183</v>
-      </c>
-      <c r="O101">
-        <v>1.847807694897959</v>
-      </c>
-      <c r="P101">
-        <v>4.415947203061224</v>
-      </c>
-      <c r="Q101">
-        <v>8.615947203061223</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.586485053917828</v>
-      </c>
-      <c r="T101">
-        <v>54.77327171132449</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.295</v>
-      </c>
-      <c r="W101">
-        <v>0.06345000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.617210530626643</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
